--- a/data/TROPONIN Dataset.xlsx
+++ b/data/TROPONIN Dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\PHD_Projects\MechanisticAI\MechanisticAI_AMI\Datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\PHD_Projects\MechanisticAI\MechanisticsAI_julia\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDCA283-6001-4B87-AF9C-01D6F03C773A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63DCC56-5203-4DAD-A224-ADB1AABF5938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8130" yWindow="3375" windowWidth="18210" windowHeight="12585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4815" windowWidth="18240" windowHeight="28320" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="STEMI_values" sheetId="4" r:id="rId3"/>
     <sheet name="NSTEMI_times" sheetId="3" r:id="rId4"/>
     <sheet name="NSTEMI_values" sheetId="5" r:id="rId5"/>
-    <sheet name="dt_2_NSTEMI working..." sheetId="6" r:id="rId6"/>
-    <sheet name="dt2_STEMI_working" sheetId="12" r:id="rId7"/>
-    <sheet name="CBRA NSTEMI working..." sheetId="7" r:id="rId8"/>
-    <sheet name="n_cbra_times_1_working" sheetId="10" r:id="rId9"/>
-    <sheet name="n_cbra_times_2_working" sheetId="11" r:id="rId10"/>
-    <sheet name="CBRA STEMI working..." sheetId="15" r:id="rId11"/>
-    <sheet name="dt3_STEMI" sheetId="16" r:id="rId12"/>
+    <sheet name="Deleted" sheetId="17" r:id="rId6"/>
+    <sheet name="dt_2_NSTEMI working..." sheetId="6" r:id="rId7"/>
+    <sheet name="dt2_STEMI_working" sheetId="12" r:id="rId8"/>
+    <sheet name="CBRA NSTEMI working..." sheetId="7" r:id="rId9"/>
+    <sheet name="n_cbra_times_1_working" sheetId="10" r:id="rId10"/>
+    <sheet name="n_cbra_times_2_working" sheetId="11" r:id="rId11"/>
+    <sheet name="CBRA STEMI working..." sheetId="15" r:id="rId12"/>
+    <sheet name="dt3_STEMI" sheetId="16" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4818" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4898" uniqueCount="1712">
   <si>
     <t>Dataset sumary</t>
   </si>
@@ -4988,6 +4989,201 @@
   </si>
   <si>
     <t xml:space="preserve"> for dataset</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Times</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Mean max value</t>
+  </si>
+  <si>
+    <t>Mean values</t>
+  </si>
+  <si>
+    <t>Mean intervals</t>
+  </si>
+  <si>
+    <t>Observation time</t>
+  </si>
+  <si>
+    <t>STEMI</t>
+  </si>
+  <si>
+    <t>NSTEMI</t>
+  </si>
+  <si>
+    <t>Before 24h</t>
+  </si>
+  <si>
+    <t>After 24h</t>
+  </si>
+  <si>
+    <t>Before 36h</t>
+  </si>
+  <si>
+    <t>After 36h</t>
+  </si>
+  <si>
+    <t>Mean time max</t>
+  </si>
+  <si>
+    <t>6.48 ± 7.44</t>
+  </si>
+  <si>
+    <t>4.33 ± 4.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.95 ± 7.39</t>
+  </si>
+  <si>
+    <t>3.54 ± 3.79</t>
+  </si>
+  <si>
+    <t>6.94 ± 7.29</t>
+  </si>
+  <si>
+    <t>16.39 ± 5.41</t>
+  </si>
+  <si>
+    <t>45.76 ± 23.48</t>
+  </si>
+  <si>
+    <t>18.79 ± 7.37</t>
+  </si>
+  <si>
+    <t>64.42 ± 21.54</t>
+  </si>
+  <si>
+    <t>6.13 ± 2.28</t>
+  </si>
+  <si>
+    <t>22.76 ± 6.92</t>
+  </si>
+  <si>
+    <t>7.04 ± 3.26</t>
+  </si>
+  <si>
+    <t>4.81 ± 5.40</t>
+  </si>
+  <si>
+    <t>2.17 ± 2.29</t>
+  </si>
+  <si>
+    <t>3.01 ± 3.03</t>
+  </si>
+  <si>
+    <t>26.05 ± 21.14</t>
+  </si>
+  <si>
+    <t>23.27 ± 7.53</t>
+  </si>
+  <si>
+    <t>18.95 ± 5.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.76 ± 5.60</t>
+  </si>
+  <si>
+    <t>2.39 ± 2.43</t>
+  </si>
+  <si>
+    <t>7.47 ± 5.39</t>
+  </si>
+  <si>
+    <t>136.38 ± 94.38</t>
+  </si>
+  <si>
+    <t>13.22 ± 6.89</t>
+  </si>
+  <si>
+    <t>121.89 ± 92.16</t>
+  </si>
+  <si>
+    <t>0.68 ± 1.20</t>
+  </si>
+  <si>
+    <t>1.09 ± 1.63</t>
+  </si>
+  <si>
+    <t>0.87 ± 1.34</t>
+  </si>
+  <si>
+    <t>1.03 ± 1.56</t>
+  </si>
+  <si>
+    <t>1.22 ± 1.80</t>
+  </si>
+  <si>
+    <t>16.70 ± 6.01</t>
+  </si>
+  <si>
+    <t>79.49 ± 89.61</t>
+  </si>
+  <si>
+    <t>21.48 ± 7.94</t>
+  </si>
+  <si>
+    <t>87.66 ± 86.69</t>
+  </si>
+  <si>
+    <t>63.18 ± 53.98</t>
+  </si>
+  <si>
+    <t>0.54 ± 0.83</t>
+  </si>
+  <si>
+    <t>0.67 ± 0.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.64 ± 0.82</t>
+  </si>
+  <si>
+    <t>0.66 ± 0.87</t>
+  </si>
+  <si>
+    <t>0.68 ± 0.89</t>
+  </si>
+  <si>
+    <t>7.73 ± 3.56</t>
+  </si>
+  <si>
+    <t>19.73 ± 3.48</t>
+  </si>
+  <si>
+    <t>7.95 ± 4.18</t>
+  </si>
+  <si>
+    <t>19.82 ± 3.46</t>
+  </si>
+  <si>
+    <t>18.64 ± 15.83</t>
+  </si>
+  <si>
+    <t>5.64 ± 6.59</t>
+  </si>
+  <si>
+    <t>96.91 ± 48.05</t>
+  </si>
+  <si>
+    <t>11.69 ± 7.86</t>
+  </si>
+  <si>
+    <t>83.11 ± 48.83</t>
+  </si>
+  <si>
+    <t>115.74 ± 89.25</t>
+  </si>
+  <si>
+    <t>154.81 ± 92.29</t>
   </si>
 </sst>
 </file>
@@ -5001,7 +5197,7 @@
     <numFmt numFmtId="167" formatCode="yy/m/d/\ hh:mm:ss;"/>
     <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5054,8 +5250,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5170,6 +5373,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -5280,7 +5501,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5351,12 +5572,66 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normale 2" xfId="1" xr:uid="{345BDDD0-3347-4871-AE91-4592EAF0DEDE}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5382,6 +5657,55 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5661,10 +5985,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -5740,14 +6064,14 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
         <f>SUM(C2:H2)</f>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J2" s="47"/>
       <c r="K2" s="43"/>
@@ -5827,7 +6151,7 @@
       </c>
       <c r="G4" s="40">
         <f>SUM(G2:G3)</f>
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="H4" s="40">
         <f>SUM(H2:H3)</f>
@@ -5835,7 +6159,7 @@
       </c>
       <c r="I4" s="40">
         <f>SUM(C4:H4)</f>
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J4" s="48"/>
       <c r="K4" s="44"/>
@@ -6770,12 +7094,3237 @@
       <c r="J40" s="49"/>
       <c r="K40" s="45"/>
     </row>
+    <row r="44" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A44" s="56" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B44" s="86" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C44" s="86"/>
+      <c r="D44" s="87" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E44" s="87"/>
+      <c r="F44" s="88" t="s">
+        <v>1659</v>
+      </c>
+      <c r="G44" s="88"/>
+      <c r="H44" s="89" t="s">
+        <v>1660</v>
+      </c>
+      <c r="I44" s="89"/>
+      <c r="J44" s="90" t="s">
+        <v>7</v>
+      </c>
+      <c r="K44" s="90"/>
+    </row>
+    <row r="45" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A45" s="91"/>
+      <c r="B45" s="92" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C45" s="93" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D45" s="92" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E45" s="93" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F45" s="92" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G45" s="93" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H45" s="92" t="s">
+        <v>1655</v>
+      </c>
+      <c r="I45" s="93" t="s">
+        <v>1656</v>
+      </c>
+      <c r="J45" s="92" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K45" s="93" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A46" s="56" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B46" s="94" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C46" s="95" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D46" s="94" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E46" s="95" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F46" s="94" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G46" s="95" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H46" s="94" t="s">
+        <v>1665</v>
+      </c>
+      <c r="I46" s="95" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J46" s="94" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K46" s="95" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A47" s="56" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C47" s="95" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D47" s="94" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E47" s="95" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F47" s="94" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G47" s="95" t="s">
+        <v>1693</v>
+      </c>
+      <c r="H47" s="94" t="s">
+        <v>1670</v>
+      </c>
+      <c r="I47" s="95" t="s">
+        <v>1694</v>
+      </c>
+      <c r="J47" s="94" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K47" s="95" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A48" s="56" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B48" s="94" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C48" s="95" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D48" s="94" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E48" s="95" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F48" s="94" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G48" s="95" t="s">
+        <v>1698</v>
+      </c>
+      <c r="H48" s="94" t="s">
+        <v>1675</v>
+      </c>
+      <c r="I48" s="95" t="s">
+        <v>1699</v>
+      </c>
+      <c r="J48" s="94" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K48" s="95" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A49" s="56" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B49" s="94" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C49" s="95" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D49" s="94" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E49" s="95" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F49" s="94" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G49" s="95" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H49" s="94" t="s">
+        <v>1678</v>
+      </c>
+      <c r="I49" s="95" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J49" s="94" t="s">
+        <v>1679</v>
+      </c>
+      <c r="K49" s="95" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="A50" s="56" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B50" s="94" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C50" s="95" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D50" s="94" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E50" s="95" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F50" s="94" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G50" s="95" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H50" s="94" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I50" s="95" t="s">
+        <v>1709</v>
+      </c>
+      <c r="J50" s="94" t="s">
+        <v>1711</v>
+      </c>
+      <c r="K50" s="95" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J44:K44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8135EEF6-3F0F-4D63-BE5A-9CDAF45EB7F7}">
+  <dimension ref="A1:T355"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J1" t="s">
+        <v>417</v>
+      </c>
+      <c r="K1" t="s">
+        <v>418</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H3" t="s">
+        <v>430</v>
+      </c>
+      <c r="I3" t="s">
+        <v>431</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" t="s">
+        <v>433</v>
+      </c>
+      <c r="F4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H4" t="s">
+        <v>436</v>
+      </c>
+      <c r="I4" t="s">
+        <v>437</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" t="s">
+        <v>439</v>
+      </c>
+      <c r="F5" t="s">
+        <v>440</v>
+      </c>
+      <c r="G5" t="s">
+        <v>441</v>
+      </c>
+      <c r="H5" t="s">
+        <v>442</v>
+      </c>
+      <c r="I5" t="s">
+        <v>443</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G6" t="s">
+        <v>447</v>
+      </c>
+      <c r="H6" t="s">
+        <v>448</v>
+      </c>
+      <c r="I6" t="s">
+        <v>449</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G7" t="s">
+        <v>453</v>
+      </c>
+      <c r="H7" t="s">
+        <v>454</v>
+      </c>
+      <c r="I7" t="s">
+        <v>455</v>
+      </c>
+      <c r="J7" t="s">
+        <v>456</v>
+      </c>
+      <c r="K7" t="s">
+        <v>457</v>
+      </c>
+      <c r="L7" t="s">
+        <v>458</v>
+      </c>
+      <c r="M7" t="s">
+        <v>459</v>
+      </c>
+      <c r="N7" t="s">
+        <v>460</v>
+      </c>
+      <c r="O7" t="s">
+        <v>461</v>
+      </c>
+      <c r="P7" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>434</v>
+      </c>
+      <c r="R7" t="s">
+        <v>436</v>
+      </c>
+      <c r="S7" t="s">
+        <v>437</v>
+      </c>
+      <c r="T7" s="20" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="D8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F8" t="s">
+        <v>464</v>
+      </c>
+      <c r="G8" t="s">
+        <v>465</v>
+      </c>
+      <c r="H8" t="s">
+        <v>466</v>
+      </c>
+      <c r="I8" t="s">
+        <v>467</v>
+      </c>
+      <c r="J8" t="s">
+        <v>468</v>
+      </c>
+      <c r="K8" t="s">
+        <v>469</v>
+      </c>
+      <c r="L8" t="s">
+        <v>470</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" t="s">
+        <v>472</v>
+      </c>
+      <c r="F9" t="s">
+        <v>472</v>
+      </c>
+      <c r="G9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H9" t="s">
+        <v>474</v>
+      </c>
+      <c r="I9" t="s">
+        <v>475</v>
+      </c>
+      <c r="J9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K9" t="s">
+        <v>477</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>421</v>
+      </c>
+      <c r="D10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" t="s">
+        <v>479</v>
+      </c>
+      <c r="F10" t="s">
+        <v>480</v>
+      </c>
+      <c r="G10" t="s">
+        <v>481</v>
+      </c>
+      <c r="H10" t="s">
+        <v>482</v>
+      </c>
+      <c r="I10" t="s">
+        <v>483</v>
+      </c>
+      <c r="J10" t="s">
+        <v>484</v>
+      </c>
+      <c r="K10" t="s">
+        <v>485</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>422</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" t="s">
+        <v>487</v>
+      </c>
+      <c r="F11" t="s">
+        <v>488</v>
+      </c>
+      <c r="G11" t="s">
+        <v>489</v>
+      </c>
+      <c r="H11" t="s">
+        <v>490</v>
+      </c>
+      <c r="I11" t="s">
+        <v>491</v>
+      </c>
+      <c r="J11" t="s">
+        <v>492</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>423</v>
+      </c>
+      <c r="D12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" t="s">
+        <v>494</v>
+      </c>
+      <c r="F12" t="s">
+        <v>495</v>
+      </c>
+      <c r="G12" t="s">
+        <v>496</v>
+      </c>
+      <c r="H12" t="s">
+        <v>497</v>
+      </c>
+      <c r="I12" t="s">
+        <v>498</v>
+      </c>
+      <c r="J12" t="s">
+        <v>499</v>
+      </c>
+      <c r="K12" t="s">
+        <v>500</v>
+      </c>
+      <c r="L12" t="s">
+        <v>501</v>
+      </c>
+      <c r="M12" t="s">
+        <v>502</v>
+      </c>
+      <c r="N12" t="s">
+        <v>503</v>
+      </c>
+      <c r="O12" t="s">
+        <v>504</v>
+      </c>
+      <c r="P12" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>424</v>
+      </c>
+      <c r="D13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" t="s">
+        <v>507</v>
+      </c>
+      <c r="F13" t="s">
+        <v>508</v>
+      </c>
+      <c r="G13" t="s">
+        <v>509</v>
+      </c>
+      <c r="H13" t="s">
+        <v>510</v>
+      </c>
+      <c r="I13" t="s">
+        <v>511</v>
+      </c>
+      <c r="J13" t="s">
+        <v>512</v>
+      </c>
+      <c r="K13" t="s">
+        <v>513</v>
+      </c>
+      <c r="L13" t="s">
+        <v>514</v>
+      </c>
+      <c r="M13" t="s">
+        <v>515</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" t="s">
+        <v>517</v>
+      </c>
+      <c r="F14" t="s">
+        <v>518</v>
+      </c>
+      <c r="G14" t="s">
+        <v>519</v>
+      </c>
+      <c r="H14" t="s">
+        <v>520</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>522</v>
+      </c>
+      <c r="F15" t="s">
+        <v>523</v>
+      </c>
+      <c r="G15" t="s">
+        <v>524</v>
+      </c>
+      <c r="H15" t="s">
+        <v>525</v>
+      </c>
+      <c r="I15" t="s">
+        <v>526</v>
+      </c>
+      <c r="J15" t="s">
+        <v>527</v>
+      </c>
+      <c r="K15" t="s">
+        <v>528</v>
+      </c>
+      <c r="L15" t="s">
+        <v>529</v>
+      </c>
+      <c r="M15" t="s">
+        <v>530</v>
+      </c>
+      <c r="N15" t="s">
+        <v>531</v>
+      </c>
+      <c r="O15" t="s">
+        <v>532</v>
+      </c>
+      <c r="P15" s="20" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>427</v>
+      </c>
+      <c r="D16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" t="s">
+        <v>534</v>
+      </c>
+      <c r="F16" t="s">
+        <v>535</v>
+      </c>
+      <c r="G16" t="s">
+        <v>536</v>
+      </c>
+      <c r="H16" t="s">
+        <v>537</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>428</v>
+      </c>
+      <c r="D17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" t="s">
+        <v>539</v>
+      </c>
+      <c r="F17" t="s">
+        <v>540</v>
+      </c>
+      <c r="G17" t="s">
+        <v>485</v>
+      </c>
+      <c r="H17" t="s">
+        <v>486</v>
+      </c>
+      <c r="I17" t="s">
+        <v>541</v>
+      </c>
+      <c r="J17" t="s">
+        <v>542</v>
+      </c>
+      <c r="K17" t="s">
+        <v>543</v>
+      </c>
+      <c r="L17" t="s">
+        <v>544</v>
+      </c>
+      <c r="M17" t="s">
+        <v>545</v>
+      </c>
+      <c r="N17" t="s">
+        <v>546</v>
+      </c>
+      <c r="O17" s="20" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>429</v>
+      </c>
+      <c r="D18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" t="s">
+        <v>548</v>
+      </c>
+      <c r="F18" t="s">
+        <v>549</v>
+      </c>
+      <c r="G18" t="s">
+        <v>550</v>
+      </c>
+      <c r="H18" t="s">
+        <v>551</v>
+      </c>
+      <c r="I18" t="s">
+        <v>552</v>
+      </c>
+      <c r="J18" t="s">
+        <v>553</v>
+      </c>
+      <c r="K18" t="s">
+        <v>554</v>
+      </c>
+      <c r="L18" t="s">
+        <v>555</v>
+      </c>
+      <c r="M18" t="s">
+        <v>556</v>
+      </c>
+      <c r="N18" t="s">
+        <v>557</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>430</v>
+      </c>
+      <c r="D19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" t="s">
+        <v>559</v>
+      </c>
+      <c r="F19" t="s">
+        <v>560</v>
+      </c>
+      <c r="G19" t="s">
+        <v>561</v>
+      </c>
+      <c r="H19" t="s">
+        <v>562</v>
+      </c>
+      <c r="I19" t="s">
+        <v>563</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>431</v>
+      </c>
+      <c r="D20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G20" t="s">
+        <v>567</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="D21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" t="s">
+        <v>569</v>
+      </c>
+      <c r="F21" t="s">
+        <v>570</v>
+      </c>
+      <c r="G21" t="s">
+        <v>571</v>
+      </c>
+      <c r="H21" t="s">
+        <v>572</v>
+      </c>
+      <c r="I21" t="s">
+        <v>573</v>
+      </c>
+      <c r="J21" t="s">
+        <v>574</v>
+      </c>
+      <c r="K21" t="s">
+        <v>575</v>
+      </c>
+      <c r="L21" t="s">
+        <v>576</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>433</v>
+      </c>
+      <c r="D22" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" t="s">
+        <v>578</v>
+      </c>
+      <c r="F22" t="s">
+        <v>579</v>
+      </c>
+      <c r="G22" t="s">
+        <v>580</v>
+      </c>
+      <c r="H22" t="s">
+        <v>581</v>
+      </c>
+      <c r="I22" t="s">
+        <v>582</v>
+      </c>
+      <c r="J22" t="s">
+        <v>583</v>
+      </c>
+      <c r="K22" t="s">
+        <v>584</v>
+      </c>
+      <c r="L22" t="s">
+        <v>585</v>
+      </c>
+      <c r="M22" t="s">
+        <v>586</v>
+      </c>
+      <c r="N22" t="s">
+        <v>587</v>
+      </c>
+      <c r="O22" t="s">
+        <v>588</v>
+      </c>
+      <c r="P22" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>434</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" t="s">
+        <v>591</v>
+      </c>
+      <c r="F23" t="s">
+        <v>592</v>
+      </c>
+      <c r="G23" t="s">
+        <v>593</v>
+      </c>
+      <c r="H23" t="s">
+        <v>549</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>435</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" t="s">
+        <v>595</v>
+      </c>
+      <c r="F24" t="s">
+        <v>596</v>
+      </c>
+      <c r="G24" t="s">
+        <v>597</v>
+      </c>
+      <c r="H24" t="s">
+        <v>598</v>
+      </c>
+      <c r="I24" t="s">
+        <v>599</v>
+      </c>
+      <c r="J24" t="s">
+        <v>600</v>
+      </c>
+      <c r="K24" t="s">
+        <v>601</v>
+      </c>
+      <c r="L24" t="s">
+        <v>602</v>
+      </c>
+      <c r="M24" t="s">
+        <v>603</v>
+      </c>
+      <c r="N24" t="s">
+        <v>604</v>
+      </c>
+      <c r="O24" t="s">
+        <v>605</v>
+      </c>
+      <c r="P24" s="20" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" t="s">
+        <v>607</v>
+      </c>
+      <c r="F25" t="s">
+        <v>608</v>
+      </c>
+      <c r="G25" t="s">
+        <v>609</v>
+      </c>
+      <c r="H25" t="s">
+        <v>610</v>
+      </c>
+      <c r="I25" t="s">
+        <v>611</v>
+      </c>
+      <c r="J25" t="s">
+        <v>612</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>437</v>
+      </c>
+      <c r="D26" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" t="s">
+        <v>614</v>
+      </c>
+      <c r="F26" t="s">
+        <v>615</v>
+      </c>
+      <c r="G26" t="s">
+        <v>616</v>
+      </c>
+      <c r="H26" t="s">
+        <v>617</v>
+      </c>
+      <c r="I26" t="s">
+        <v>618</v>
+      </c>
+      <c r="J26" t="s">
+        <v>619</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="D27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" t="s">
+        <v>621</v>
+      </c>
+      <c r="F27" t="s">
+        <v>622</v>
+      </c>
+      <c r="G27" t="s">
+        <v>623</v>
+      </c>
+      <c r="H27" t="s">
+        <v>624</v>
+      </c>
+      <c r="I27" t="s">
+        <v>625</v>
+      </c>
+      <c r="J27" t="s">
+        <v>626</v>
+      </c>
+      <c r="K27" t="s">
+        <v>627</v>
+      </c>
+      <c r="L27" t="s">
+        <v>628</v>
+      </c>
+      <c r="M27" t="s">
+        <v>629</v>
+      </c>
+      <c r="N27" t="s">
+        <v>630</v>
+      </c>
+      <c r="O27" t="s">
+        <v>631</v>
+      </c>
+      <c r="P27" s="20" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>439</v>
+      </c>
+      <c r="D28" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" t="s">
+        <v>633</v>
+      </c>
+      <c r="F28" t="s">
+        <v>634</v>
+      </c>
+      <c r="G28" t="s">
+        <v>634</v>
+      </c>
+      <c r="H28" t="s">
+        <v>635</v>
+      </c>
+      <c r="I28" t="s">
+        <v>636</v>
+      </c>
+      <c r="J28" t="s">
+        <v>637</v>
+      </c>
+      <c r="K28" t="s">
+        <v>638</v>
+      </c>
+      <c r="L28" t="s">
+        <v>639</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>440</v>
+      </c>
+      <c r="D29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" t="s">
+        <v>641</v>
+      </c>
+      <c r="F29" t="s">
+        <v>642</v>
+      </c>
+      <c r="G29" t="s">
+        <v>643</v>
+      </c>
+      <c r="H29" t="s">
+        <v>644</v>
+      </c>
+      <c r="I29" t="s">
+        <v>645</v>
+      </c>
+      <c r="J29" t="s">
+        <v>646</v>
+      </c>
+      <c r="K29" t="s">
+        <v>647</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>441</v>
+      </c>
+      <c r="D30" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" t="s">
+        <v>649</v>
+      </c>
+      <c r="F30" t="s">
+        <v>650</v>
+      </c>
+      <c r="G30" t="s">
+        <v>651</v>
+      </c>
+      <c r="H30" t="s">
+        <v>652</v>
+      </c>
+      <c r="I30" t="s">
+        <v>653</v>
+      </c>
+      <c r="J30" t="s">
+        <v>654</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>442</v>
+      </c>
+      <c r="D31" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>656</v>
+      </c>
+      <c r="F31" t="s">
+        <v>657</v>
+      </c>
+      <c r="G31" t="s">
+        <v>658</v>
+      </c>
+      <c r="H31" t="s">
+        <v>659</v>
+      </c>
+      <c r="I31" t="s">
+        <v>660</v>
+      </c>
+      <c r="J31" t="s">
+        <v>661</v>
+      </c>
+      <c r="K31" t="s">
+        <v>662</v>
+      </c>
+      <c r="L31" t="s">
+        <v>663</v>
+      </c>
+      <c r="M31" t="s">
+        <v>664</v>
+      </c>
+      <c r="N31" s="20" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>443</v>
+      </c>
+      <c r="D32" t="s">
+        <v>170</v>
+      </c>
+      <c r="E32" t="s">
+        <v>666</v>
+      </c>
+      <c r="F32" t="s">
+        <v>667</v>
+      </c>
+      <c r="G32" t="s">
+        <v>668</v>
+      </c>
+      <c r="H32" t="s">
+        <v>669</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>671</v>
+      </c>
+      <c r="F33" t="s">
+        <v>659</v>
+      </c>
+      <c r="G33" t="s">
+        <v>672</v>
+      </c>
+      <c r="H33" t="s">
+        <v>660</v>
+      </c>
+      <c r="I33" t="s">
+        <v>661</v>
+      </c>
+      <c r="J33" t="s">
+        <v>663</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>445</v>
+      </c>
+      <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" t="s">
+        <v>673</v>
+      </c>
+      <c r="F34" t="s">
+        <v>674</v>
+      </c>
+      <c r="G34" t="s">
+        <v>675</v>
+      </c>
+      <c r="H34" t="s">
+        <v>676</v>
+      </c>
+      <c r="I34" t="s">
+        <v>677</v>
+      </c>
+      <c r="J34" t="s">
+        <v>678</v>
+      </c>
+      <c r="K34" t="s">
+        <v>679</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>446</v>
+      </c>
+      <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>681</v>
+      </c>
+      <c r="F35" t="s">
+        <v>682</v>
+      </c>
+      <c r="G35" t="s">
+        <v>683</v>
+      </c>
+      <c r="H35" t="s">
+        <v>684</v>
+      </c>
+      <c r="I35" t="s">
+        <v>685</v>
+      </c>
+      <c r="J35" t="s">
+        <v>686</v>
+      </c>
+      <c r="K35" t="s">
+        <v>687</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>447</v>
+      </c>
+      <c r="D36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" t="s">
+        <v>689</v>
+      </c>
+      <c r="F36" t="s">
+        <v>690</v>
+      </c>
+      <c r="G36" t="s">
+        <v>691</v>
+      </c>
+      <c r="H36" t="s">
+        <v>692</v>
+      </c>
+      <c r="I36" t="s">
+        <v>693</v>
+      </c>
+      <c r="J36" t="s">
+        <v>694</v>
+      </c>
+      <c r="K36" t="s">
+        <v>695</v>
+      </c>
+      <c r="L36" t="s">
+        <v>696</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>448</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
+        <v>698</v>
+      </c>
+      <c r="F37" t="s">
+        <v>699</v>
+      </c>
+      <c r="G37" t="s">
+        <v>700</v>
+      </c>
+      <c r="H37" t="s">
+        <v>701</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>449</v>
+      </c>
+      <c r="D38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E38" t="s">
+        <v>703</v>
+      </c>
+      <c r="F38" t="s">
+        <v>704</v>
+      </c>
+      <c r="G38" t="s">
+        <v>705</v>
+      </c>
+      <c r="H38" t="s">
+        <v>537</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="D39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" t="s">
+        <v>706</v>
+      </c>
+      <c r="F39" t="s">
+        <v>707</v>
+      </c>
+      <c r="G39" t="s">
+        <v>708</v>
+      </c>
+      <c r="H39" t="s">
+        <v>709</v>
+      </c>
+      <c r="I39" t="s">
+        <v>710</v>
+      </c>
+      <c r="J39" t="s">
+        <v>711</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>451</v>
+      </c>
+      <c r="D40" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" t="s">
+        <v>713</v>
+      </c>
+      <c r="F40" t="s">
+        <v>714</v>
+      </c>
+      <c r="G40" t="s">
+        <v>715</v>
+      </c>
+      <c r="H40" t="s">
+        <v>716</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>452</v>
+      </c>
+      <c r="D41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E41" t="s">
+        <v>718</v>
+      </c>
+      <c r="F41" t="s">
+        <v>719</v>
+      </c>
+      <c r="G41" t="s">
+        <v>720</v>
+      </c>
+      <c r="H41" t="s">
+        <v>721</v>
+      </c>
+      <c r="I41" t="s">
+        <v>722</v>
+      </c>
+      <c r="J41" t="s">
+        <v>723</v>
+      </c>
+      <c r="K41" t="s">
+        <v>724</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>453</v>
+      </c>
+      <c r="D42" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" t="s">
+        <v>726</v>
+      </c>
+      <c r="F42" t="s">
+        <v>727</v>
+      </c>
+      <c r="G42" t="s">
+        <v>421</v>
+      </c>
+      <c r="H42" t="s">
+        <v>422</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>454</v>
+      </c>
+      <c r="D43" t="s">
+        <v>181</v>
+      </c>
+      <c r="E43" t="s">
+        <v>728</v>
+      </c>
+      <c r="F43" t="s">
+        <v>729</v>
+      </c>
+      <c r="G43" t="s">
+        <v>730</v>
+      </c>
+      <c r="H43" t="s">
+        <v>731</v>
+      </c>
+      <c r="I43" t="s">
+        <v>732</v>
+      </c>
+      <c r="J43" t="s">
+        <v>733</v>
+      </c>
+      <c r="K43" t="s">
+        <v>734</v>
+      </c>
+      <c r="L43" t="s">
+        <v>735</v>
+      </c>
+      <c r="M43" t="s">
+        <v>736</v>
+      </c>
+      <c r="N43" t="s">
+        <v>737</v>
+      </c>
+      <c r="O43" t="s">
+        <v>738</v>
+      </c>
+      <c r="P43" s="20" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>455</v>
+      </c>
+      <c r="D44" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" t="s">
+        <v>740</v>
+      </c>
+      <c r="F44" t="s">
+        <v>741</v>
+      </c>
+      <c r="G44" t="s">
+        <v>742</v>
+      </c>
+      <c r="H44" t="s">
+        <v>743</v>
+      </c>
+      <c r="I44" t="s">
+        <v>744</v>
+      </c>
+      <c r="J44" t="s">
+        <v>745</v>
+      </c>
+      <c r="K44" t="s">
+        <v>746</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>456</v>
+      </c>
+      <c r="D45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="20" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="20" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="20" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="20" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="20" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="20" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="20" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="20" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="20" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="20" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="20" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="20" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="20" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="20" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="20" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="20" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="20" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="20" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="20" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="20" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="20" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="20" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="20" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="20" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="20" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="20" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="20" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="20" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="20" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="20" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="20" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="20" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="20" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="20" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="20" t="s">
+        <v>747</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A4CC72-F639-4BA7-ACD7-5204AC2BE402}">
   <dimension ref="A1:U139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12808,7 +16357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EE65CFF-C8D1-44A0-BB31-1A83C82D1538}">
   <dimension ref="A1:AI510"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -29875,7 +33424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63622D53-31C3-4AFC-B165-6AEDB8EB995F}">
   <dimension ref="A1:AE56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34289,18 +37838,15 @@
         <v>105.94999999995343</v>
       </c>
       <c r="I51" s="1">
-        <v>122.03333333332557</v>
+        <v>147.19999999995343</v>
       </c>
       <c r="J51" s="1">
-        <v>147.19999999995343</v>
-      </c>
-      <c r="K51" s="1">
         <v>170.25</v>
       </c>
+      <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -34534,16 +38080,13 @@
         <v>138.86666666669771</v>
       </c>
       <c r="I58" s="1">
-        <v>162.40000000008149</v>
-      </c>
-      <c r="J58" s="1">
         <v>189.56666666676756</v>
       </c>
+      <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -36927,6 +40470,16 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:X50 B52:X57 B59:X129">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>B1=MAX($B1:$X1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51:W51 B58:W58">
+    <cfRule type="expression" dxfId="11" priority="8">
+      <formula>B51=MAX($B51:$W51)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -38465,7 +42018,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="4" t="s">
         <v>799</v>
       </c>
       <c r="B51">
@@ -38489,13 +42042,10 @@
       <c r="H51">
         <v>2.36</v>
       </c>
-      <c r="I51" s="31">
-        <v>42553</v>
+      <c r="I51">
+        <v>1.91</v>
       </c>
       <c r="J51">
-        <v>1.91</v>
-      </c>
-      <c r="K51">
         <v>1.56</v>
       </c>
     </row>
@@ -38668,7 +42218,7 @@
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="4" t="s">
         <v>806</v>
       </c>
       <c r="B58">
@@ -38692,10 +42242,7 @@
       <c r="H58">
         <v>5.1100000000000003</v>
       </c>
-      <c r="I58" s="31">
-        <v>42645</v>
-      </c>
-      <c r="J58">
+      <c r="I58">
         <v>0.75800000000000001</v>
       </c>
     </row>
@@ -41044,13 +44591,28 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:X50 B52:X57 B59:X129">
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>B1=MAX($B1:$X1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51:W51 B58:W58">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>B51=MAX($B51:$W51)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:X129">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>B1&gt;100</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{946518B8-EFF0-48A5-A6DF-BB3DA6B834E9}">
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -42718,7 +46280,7 @@
         <v>96.049999999988358</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -42741,7 +46303,7 @@
         <v>96.149999999965075</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>144</v>
       </c>
@@ -42764,7 +46326,7 @@
         <v>96.083333333255723</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>145</v>
       </c>
@@ -42805,19 +46367,16 @@
         <v>192.08333333325572</v>
       </c>
       <c r="N67">
-        <v>216.26666666666279</v>
+        <v>240.21666666667443</v>
       </c>
       <c r="O67">
-        <v>240.21666666667443</v>
+        <v>264.18333333340706</v>
       </c>
       <c r="P67">
-        <v>264.18333333340706</v>
-      </c>
-      <c r="Q67">
         <v>288.04999999998836</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -42849,7 +46408,7 @@
         <v>144.1333333334187</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -42878,7 +46437,7 @@
         <v>144.09999999997672</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>149</v>
       </c>
@@ -42904,7 +46463,7 @@
         <v>120.04999999998836</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>150</v>
       </c>
@@ -42944,11 +46503,8 @@
       <c r="M71">
         <v>192.65000000002328</v>
       </c>
-      <c r="N71">
-        <v>221.68333333334886</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>151</v>
       </c>
@@ -42983,7 +46539,7 @@
         <v>173.78333333332557</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>152</v>
       </c>
@@ -43003,7 +46559,7 @@
         <v>48.099999999976717</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>153</v>
       </c>
@@ -43023,7 +46579,7 @@
         <v>72.016666666720994</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>154</v>
       </c>
@@ -43049,7 +46605,7 @@
         <v>96.333333333372138</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>155</v>
       </c>
@@ -43069,7 +46625,7 @@
         <v>48.183333333407063</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>156</v>
       </c>
@@ -43107,7 +46663,7 @@
         <v>192.1333333334187</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>157</v>
       </c>
@@ -43145,7 +46701,7 @@
         <v>168.04999999998836</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>158</v>
       </c>
@@ -43168,7 +46724,7 @@
         <v>96.049999999988358</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -43185,7 +46741,7 @@
         <v>48.133333333418705</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -43214,442 +46770,418 @@
         <v>168.03333333326736</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82">
-        <v>4.3500000000349246</v>
+        <v>11.100000000034925</v>
       </c>
       <c r="C82">
-        <v>4.3666666665812954</v>
+        <v>17.150000000023283</v>
       </c>
       <c r="D82">
-        <v>15.650000000023283</v>
+        <v>24.266666666662786</v>
       </c>
       <c r="E82">
-        <v>24.450000000069849</v>
+        <v>48.866666666697711</v>
       </c>
       <c r="F82">
-        <v>48.433333333348855</v>
-      </c>
-      <c r="G82">
-        <v>72.199999999953434</v>
-      </c>
-      <c r="H82">
-        <v>96.883333333418705</v>
-      </c>
-      <c r="I82">
-        <v>120.76666666672099</v>
-      </c>
-      <c r="J82">
-        <v>144.21666666667443</v>
-      </c>
-      <c r="K82">
-        <v>168.03333333326736</v>
-      </c>
-      <c r="L82">
-        <v>192.09999999997672</v>
-      </c>
-      <c r="M82">
-        <v>216.23333333339542</v>
-      </c>
-      <c r="N82">
-        <v>265.48333333327901</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+        <v>72.066666666709352</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83">
-        <v>11.100000000034925</v>
+        <v>7.0999999999185093</v>
       </c>
       <c r="C83">
-        <v>17.150000000023283</v>
+        <v>7.1333333333604969</v>
       </c>
       <c r="D83">
+        <v>17.733333333337214</v>
+      </c>
+      <c r="E83">
+        <v>24.149999999965075</v>
+      </c>
+      <c r="F83">
+        <v>48.083333333255723</v>
+      </c>
+      <c r="G83">
+        <v>72.266666666662786</v>
+      </c>
+      <c r="H83">
+        <v>96.566666666592937</v>
+      </c>
+      <c r="I83">
+        <v>120.46666666661622</v>
+      </c>
+      <c r="J83">
+        <v>144.98333333339542</v>
+      </c>
+      <c r="K83">
+        <v>145.1166666666395</v>
+      </c>
+      <c r="L83">
+        <v>168.08333333325572</v>
+      </c>
+      <c r="M83">
+        <v>192.03333333326736</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84">
+        <v>6.3833333333604969</v>
+      </c>
+      <c r="C84">
+        <v>6.4000000000814907</v>
+      </c>
+      <c r="D84">
+        <v>15.500000000058208</v>
+      </c>
+      <c r="E84">
         <v>24.266666666662786</v>
       </c>
-      <c r="E83">
-        <v>48.866666666697711</v>
-      </c>
-      <c r="F83">
-        <v>72.066666666709352</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>163</v>
-      </c>
-      <c r="B84">
-        <v>7.0999999999185093</v>
-      </c>
-      <c r="C84">
-        <v>7.1333333333604969</v>
-      </c>
-      <c r="D84">
+      <c r="F84">
+        <v>48.099999999976717</v>
+      </c>
+      <c r="G84">
+        <v>73.066666666651145</v>
+      </c>
+      <c r="H84">
+        <v>96.166666666686069</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>165</v>
+      </c>
+      <c r="B85">
+        <v>17.633333333360497</v>
+      </c>
+      <c r="C85">
+        <v>24.183333333407063</v>
+      </c>
+      <c r="D85">
+        <v>38.866666666581295</v>
+      </c>
+      <c r="E85">
+        <v>48.133333333418705</v>
+      </c>
+      <c r="F85">
+        <v>72.216666666674428</v>
+      </c>
+      <c r="G85">
+        <v>96.066666666709352</v>
+      </c>
+      <c r="H85">
+        <v>120.01666666672099</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86">
+        <v>4.7499999999417923</v>
+      </c>
+      <c r="C86">
+        <v>10.133333333360497</v>
+      </c>
+      <c r="D86">
         <v>17.733333333337214</v>
       </c>
-      <c r="E84">
+      <c r="E86">
+        <v>24.566666666592937</v>
+      </c>
+      <c r="F86">
+        <v>48.566666666592937</v>
+      </c>
+      <c r="G86">
+        <v>78.299999999930151</v>
+      </c>
+      <c r="H86">
+        <v>102.28333333338378</v>
+      </c>
+      <c r="I86">
+        <v>120.03333333326736</v>
+      </c>
+      <c r="J86">
+        <v>144.06666666670935</v>
+      </c>
+      <c r="K86">
+        <v>173.88333333330229</v>
+      </c>
+      <c r="L86">
+        <v>192.04999999998836</v>
+      </c>
+      <c r="M86">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87">
+        <v>5.9833333332790062</v>
+      </c>
+      <c r="C87">
+        <v>18.199999999953434</v>
+      </c>
+      <c r="D87">
         <v>24.149999999965075</v>
       </c>
-      <c r="F84">
-        <v>48.083333333255723</v>
-      </c>
-      <c r="G84">
-        <v>72.266666666662786</v>
-      </c>
-      <c r="H84">
+      <c r="E87">
+        <v>48.033333333267365</v>
+      </c>
+      <c r="F87">
+        <v>72.28333333338378</v>
+      </c>
+      <c r="G87">
+        <v>90.199999999953434</v>
+      </c>
+      <c r="H87">
+        <v>96.316666666651145</v>
+      </c>
+      <c r="I87">
+        <v>125.81666666659294</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88">
+        <v>13.21666666661622</v>
+      </c>
+      <c r="C88">
+        <v>21.849999999976717</v>
+      </c>
+      <c r="D88">
+        <v>24.083333333255723</v>
+      </c>
+      <c r="E88">
+        <v>48.183333333407063</v>
+      </c>
+      <c r="F88">
+        <v>64.666666666686069</v>
+      </c>
+      <c r="G88">
+        <v>72.133333333418705</v>
+      </c>
+      <c r="H88">
         <v>96.566666666592937</v>
       </c>
-      <c r="I84">
-        <v>120.46666666661622</v>
-      </c>
-      <c r="J84">
-        <v>144.98333333339542</v>
-      </c>
-      <c r="K84">
-        <v>145.1166666666395</v>
-      </c>
-      <c r="L84">
-        <v>168.08333333325572</v>
-      </c>
-      <c r="M84">
-        <v>192.03333333326736</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>164</v>
-      </c>
-      <c r="B85">
-        <v>6.3833333333604969</v>
-      </c>
-      <c r="C85">
-        <v>6.4000000000814907</v>
-      </c>
-      <c r="D85">
-        <v>15.500000000058208</v>
-      </c>
-      <c r="E85">
-        <v>24.266666666662786</v>
-      </c>
-      <c r="F85">
-        <v>48.099999999976717</v>
-      </c>
-      <c r="G85">
-        <v>73.066666666651145</v>
-      </c>
-      <c r="H85">
-        <v>96.166666666686069</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>165</v>
-      </c>
-      <c r="B86">
-        <v>17.633333333360497</v>
-      </c>
-      <c r="C86">
-        <v>24.183333333407063</v>
-      </c>
-      <c r="D86">
-        <v>38.866666666581295</v>
-      </c>
-      <c r="E86">
-        <v>48.133333333418705</v>
-      </c>
-      <c r="F86">
-        <v>72.216666666674428</v>
-      </c>
-      <c r="G86">
-        <v>96.066666666709352</v>
-      </c>
-      <c r="H86">
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>170</v>
+      </c>
+      <c r="B89">
+        <v>17.800000000046566</v>
+      </c>
+      <c r="C89">
+        <v>24.400000000081491</v>
+      </c>
+      <c r="D89">
+        <v>41.53333333338378</v>
+      </c>
+      <c r="E89">
+        <v>48.366666666639503</v>
+      </c>
+      <c r="F89">
+        <v>72.566666666592937</v>
+      </c>
+      <c r="G89">
+        <v>96.450000000069849</v>
+      </c>
+      <c r="H89">
+        <v>113.33333333325572</v>
+      </c>
+      <c r="I89">
         <v>120.01666666672099</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>166</v>
-      </c>
-      <c r="B87">
-        <v>4.7499999999417923</v>
-      </c>
-      <c r="C87">
-        <v>10.133333333360497</v>
-      </c>
-      <c r="D87">
-        <v>17.733333333337214</v>
-      </c>
-      <c r="E87">
-        <v>24.566666666592937</v>
-      </c>
-      <c r="F87">
+      <c r="J89">
+        <v>144.04999999998836</v>
+      </c>
+      <c r="K89">
+        <v>173.59999999991851</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90">
+        <v>11.549999999930151</v>
+      </c>
+      <c r="C90">
+        <v>21.716666666732635</v>
+      </c>
+      <c r="D90">
+        <v>24.400000000081491</v>
+      </c>
+      <c r="E90">
+        <v>48.216666666674428</v>
+      </c>
+      <c r="F90">
+        <v>72.433333333348855</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>172</v>
+      </c>
+      <c r="B91">
+        <v>23.066666666592937</v>
+      </c>
+      <c r="C91">
+        <v>24.366666666639503</v>
+      </c>
+      <c r="D91">
+        <v>41.349999999976717</v>
+      </c>
+      <c r="E91">
         <v>48.566666666592937</v>
       </c>
-      <c r="G87">
-        <v>78.299999999930151</v>
-      </c>
-      <c r="H87">
-        <v>102.28333333338378</v>
-      </c>
-      <c r="I87">
+      <c r="F91">
+        <v>72.450000000069849</v>
+      </c>
+      <c r="G91">
+        <v>96.016666666720994</v>
+      </c>
+      <c r="H91">
+        <v>120.04999999998836</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>173</v>
+      </c>
+      <c r="B92">
+        <v>20.366666666697711</v>
+      </c>
+      <c r="C92">
+        <v>29.966666666732635</v>
+      </c>
+      <c r="D92">
+        <v>35.933333333290648</v>
+      </c>
+      <c r="E92">
+        <v>48.233333333395422</v>
+      </c>
+      <c r="F92">
+        <v>72.400000000081491</v>
+      </c>
+      <c r="G92">
+        <v>96</v>
+      </c>
+      <c r="H92">
         <v>120.03333333326736</v>
       </c>
-      <c r="J87">
-        <v>144.06666666670935</v>
-      </c>
-      <c r="K87">
-        <v>173.88333333330229</v>
-      </c>
-      <c r="L87">
-        <v>192.04999999998836</v>
-      </c>
-      <c r="M87">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>168</v>
-      </c>
-      <c r="B88">
-        <v>5.9833333332790062</v>
-      </c>
-      <c r="C88">
-        <v>18.199999999953434</v>
-      </c>
-      <c r="D88">
-        <v>24.149999999965075</v>
-      </c>
-      <c r="E88">
-        <v>48.033333333267365</v>
-      </c>
-      <c r="F88">
-        <v>72.28333333338378</v>
-      </c>
-      <c r="G88">
-        <v>90.199999999953434</v>
-      </c>
-      <c r="H88">
-        <v>96.316666666651145</v>
-      </c>
-      <c r="I88">
-        <v>125.81666666659294</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>169</v>
-      </c>
-      <c r="B89">
-        <v>13.21666666661622</v>
-      </c>
-      <c r="C89">
-        <v>21.849999999976717</v>
-      </c>
-      <c r="D89">
-        <v>24.083333333255723</v>
-      </c>
-      <c r="E89">
-        <v>48.183333333407063</v>
-      </c>
-      <c r="F89">
-        <v>64.666666666686069</v>
-      </c>
-      <c r="G89">
-        <v>72.133333333418705</v>
-      </c>
-      <c r="H89">
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>174</v>
+      </c>
+      <c r="B93">
+        <v>11.000000000058208</v>
+      </c>
+      <c r="C93">
+        <v>24.28333333338378</v>
+      </c>
+      <c r="D93">
+        <v>43.233333333337214</v>
+      </c>
+      <c r="E93">
+        <v>48.166666666686069</v>
+      </c>
+      <c r="F93">
+        <v>72.349999999918509</v>
+      </c>
+      <c r="G93">
+        <v>96.216666666674428</v>
+      </c>
+      <c r="H93">
+        <v>120.18333333340706</v>
+      </c>
+      <c r="I93">
+        <v>144.08333333325572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>175</v>
+      </c>
+      <c r="B94">
+        <v>20.133333333302289</v>
+      </c>
+      <c r="C94">
+        <v>27.216666666674428</v>
+      </c>
+      <c r="D94">
+        <v>27.533333333325572</v>
+      </c>
+      <c r="E94">
+        <v>39.366666666639503</v>
+      </c>
+      <c r="F94">
+        <v>49.099999999918509</v>
+      </c>
+      <c r="G94">
+        <v>72.299999999930151</v>
+      </c>
+      <c r="H94">
         <v>96.566666666592937</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>170</v>
-      </c>
-      <c r="B90">
-        <v>17.800000000046566</v>
-      </c>
-      <c r="C90">
-        <v>24.400000000081491</v>
-      </c>
-      <c r="D90">
-        <v>41.53333333338378</v>
-      </c>
-      <c r="E90">
-        <v>48.366666666639503</v>
-      </c>
-      <c r="F90">
-        <v>72.566666666592937</v>
-      </c>
-      <c r="G90">
-        <v>96.450000000069849</v>
-      </c>
-      <c r="H90">
-        <v>113.33333333325572</v>
-      </c>
-      <c r="I90">
-        <v>120.01666666672099</v>
-      </c>
-      <c r="J90">
-        <v>144.04999999998836</v>
-      </c>
-      <c r="K90">
-        <v>173.59999999991851</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>171</v>
-      </c>
-      <c r="B91">
-        <v>11.549999999930151</v>
-      </c>
-      <c r="C91">
-        <v>21.716666666732635</v>
-      </c>
-      <c r="D91">
-        <v>24.400000000081491</v>
-      </c>
-      <c r="E91">
-        <v>48.216666666674428</v>
-      </c>
-      <c r="F91">
-        <v>72.433333333348855</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>172</v>
-      </c>
-      <c r="B92">
-        <v>23.066666666592937</v>
-      </c>
-      <c r="C92">
-        <v>24.366666666639503</v>
-      </c>
-      <c r="D92">
-        <v>41.349999999976717</v>
-      </c>
-      <c r="E92">
-        <v>48.566666666592937</v>
-      </c>
-      <c r="F92">
-        <v>72.450000000069849</v>
-      </c>
-      <c r="G92">
-        <v>96.016666666720994</v>
-      </c>
-      <c r="H92">
+      <c r="I94">
         <v>120.04999999998836</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>173</v>
-      </c>
-      <c r="B93">
-        <v>20.366666666697711</v>
-      </c>
-      <c r="C93">
-        <v>29.966666666732635</v>
-      </c>
-      <c r="D93">
-        <v>35.933333333290648</v>
-      </c>
-      <c r="E93">
-        <v>48.233333333395422</v>
-      </c>
-      <c r="F93">
-        <v>72.400000000081491</v>
-      </c>
-      <c r="G93">
-        <v>96</v>
-      </c>
-      <c r="H93">
-        <v>120.03333333326736</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>174</v>
-      </c>
-      <c r="B94">
-        <v>11.000000000058208</v>
-      </c>
-      <c r="C94">
-        <v>24.28333333338378</v>
-      </c>
-      <c r="D94">
-        <v>43.233333333337214</v>
-      </c>
-      <c r="E94">
-        <v>48.166666666686069</v>
-      </c>
-      <c r="F94">
-        <v>72.349999999918509</v>
-      </c>
-      <c r="G94">
-        <v>96.216666666674428</v>
-      </c>
-      <c r="H94">
-        <v>120.18333333340706</v>
-      </c>
-      <c r="I94">
-        <v>144.08333333325572</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J94">
+        <v>144.18333333340706</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B95">
-        <v>20.133333333302289</v>
+        <v>13.833333333372138</v>
       </c>
       <c r="C95">
-        <v>27.216666666674428</v>
+        <v>24.733333333279006</v>
       </c>
       <c r="D95">
-        <v>27.533333333325572</v>
+        <v>48.149999999965075</v>
       </c>
       <c r="E95">
-        <v>39.366666666639503</v>
+        <v>64.166666666627862</v>
       </c>
       <c r="F95">
-        <v>49.099999999918509</v>
-      </c>
-      <c r="G95">
-        <v>72.299999999930151</v>
-      </c>
-      <c r="H95">
-        <v>96.566666666592937</v>
-      </c>
-      <c r="I95">
-        <v>120.04999999998836</v>
-      </c>
-      <c r="J95">
-        <v>144.18333333340706</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+        <v>72.183333333407063</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B96">
-        <v>13.833333333372138</v>
+        <v>20.53333333338378</v>
       </c>
       <c r="C96">
-        <v>24.733333333279006</v>
+        <v>23.816666666592937</v>
       </c>
       <c r="D96">
-        <v>48.149999999965075</v>
+        <v>24.500000000058208</v>
       </c>
       <c r="E96">
-        <v>64.166666666627862</v>
+        <v>48.333333333372138</v>
       </c>
       <c r="F96">
         <v>72.183333333407063</v>
@@ -43657,190 +47189,180 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B97">
-        <v>20.53333333338378</v>
+        <v>21.166666666686069</v>
       </c>
       <c r="C97">
-        <v>23.816666666592937</v>
+        <v>24.583333333313931</v>
       </c>
       <c r="D97">
-        <v>24.500000000058208</v>
+        <v>39.983333333395422</v>
       </c>
       <c r="E97">
-        <v>48.333333333372138</v>
+        <v>48.083333333255723</v>
       </c>
       <c r="F97">
-        <v>72.183333333407063</v>
+        <v>72.049999999988358</v>
+      </c>
+      <c r="G97">
+        <v>96.333333333372138</v>
+      </c>
+      <c r="H97">
+        <v>120.06666666670935</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B98">
-        <v>21.166666666686069</v>
+        <v>16.03333333338378</v>
       </c>
       <c r="C98">
-        <v>24.583333333313931</v>
+        <v>24.516666666604578</v>
       </c>
       <c r="D98">
-        <v>39.983333333395422</v>
+        <v>40.350000000034925</v>
       </c>
       <c r="E98">
-        <v>48.083333333255723</v>
+        <v>48.650000000023283</v>
       </c>
       <c r="F98">
-        <v>72.049999999988358</v>
-      </c>
-      <c r="G98">
-        <v>96.333333333372138</v>
-      </c>
-      <c r="H98">
-        <v>120.06666666670935</v>
+        <v>72.083333333255723</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B99">
-        <v>16.03333333338378</v>
+        <v>14.833333333313931</v>
       </c>
       <c r="C99">
-        <v>24.516666666604578</v>
+        <v>21.416666666627862</v>
       </c>
       <c r="D99">
-        <v>40.350000000034925</v>
+        <v>24.949999999953434</v>
       </c>
       <c r="E99">
-        <v>48.650000000023283</v>
+        <v>48.083333333255723</v>
       </c>
       <c r="F99">
-        <v>72.083333333255723</v>
+        <v>66.783333333267365</v>
+      </c>
+      <c r="G99">
+        <v>72.400000000081491</v>
+      </c>
+      <c r="H99">
+        <v>96.149999999965075</v>
+      </c>
+      <c r="I99">
+        <v>120.04999999998836</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B100">
-        <v>14.833333333313931</v>
+        <v>12.166666666686069</v>
       </c>
       <c r="C100">
-        <v>21.416666666627862</v>
+        <v>16.733333333395422</v>
       </c>
       <c r="D100">
-        <v>24.949999999953434</v>
+        <v>24.249999999941792</v>
       </c>
       <c r="E100">
-        <v>48.083333333255723</v>
+        <v>48.149999999965075</v>
       </c>
       <c r="F100">
-        <v>66.783333333267365</v>
-      </c>
-      <c r="G100">
-        <v>72.400000000081491</v>
-      </c>
-      <c r="H100">
-        <v>96.149999999965075</v>
-      </c>
-      <c r="I100">
-        <v>120.04999999998836</v>
+        <v>72.299999999930151</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B101">
-        <v>12.166666666686069</v>
+        <v>12.916666666686069</v>
       </c>
       <c r="C101">
-        <v>16.733333333395422</v>
+        <v>30.299999999930151</v>
       </c>
       <c r="D101">
-        <v>24.249999999941792</v>
+        <v>48.083333333255723</v>
       </c>
       <c r="E101">
-        <v>48.149999999965075</v>
+        <v>78.349999999918509</v>
       </c>
       <c r="F101">
-        <v>72.299999999930151</v>
+        <v>83.616666666639503</v>
+      </c>
+      <c r="G101">
+        <v>101.90000000002328</v>
+      </c>
+      <c r="H101">
+        <v>120.1333333334187</v>
+      </c>
+      <c r="I101">
+        <v>150.14999999996508</v>
+      </c>
+      <c r="J101">
+        <v>168.1333333334187</v>
+      </c>
+      <c r="K101">
+        <v>185.81666666659294</v>
+      </c>
+      <c r="L101">
+        <v>197.44999999995343</v>
+      </c>
+      <c r="M101">
+        <v>216.16666666668607</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B102">
-        <v>12.916666666686069</v>
+        <v>8.1000000000349246</v>
       </c>
       <c r="C102">
-        <v>30.299999999930151</v>
+        <v>24.400000000081491</v>
       </c>
       <c r="D102">
-        <v>48.083333333255723</v>
+        <v>64.950000000069849</v>
       </c>
       <c r="E102">
-        <v>78.349999999918509</v>
+        <v>77.650000000081491</v>
       </c>
       <c r="F102">
-        <v>83.616666666639503</v>
+        <v>101.59999999991851</v>
       </c>
       <c r="G102">
-        <v>101.90000000002328</v>
+        <v>121.18333333334886</v>
       </c>
       <c r="H102">
-        <v>120.1333333334187</v>
-      </c>
-      <c r="I102">
-        <v>150.14999999996508</v>
-      </c>
-      <c r="J102">
-        <v>168.1333333334187</v>
-      </c>
-      <c r="K102">
-        <v>185.81666666659294</v>
-      </c>
-      <c r="L102">
-        <v>197.44999999995343</v>
-      </c>
-      <c r="M102">
-        <v>216.16666666668607</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>183</v>
-      </c>
-      <c r="B103">
-        <v>8.1000000000349246</v>
-      </c>
-      <c r="C103">
-        <v>24.400000000081491</v>
-      </c>
-      <c r="D103">
-        <v>64.950000000069849</v>
-      </c>
-      <c r="E103">
-        <v>77.650000000081491</v>
-      </c>
-      <c r="F103">
-        <v>101.59999999991851</v>
-      </c>
-      <c r="G103">
-        <v>121.18333333334886</v>
-      </c>
-      <c r="H103">
         <v>144.70000000001164</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:Q103">
-    <cfRule type="expression" dxfId="3" priority="1">
+  <conditionalFormatting sqref="B67:M67">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>COUNTIF($A67:$P67,A67)&gt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:Q66 B68:Q102">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>COUNTIF($A1:$Q1,A1)&gt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N67:P67">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>COUNTIF($A67:$P67,#REF!)&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -43849,7 +47371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E8894F-0966-4544-8672-D238E9402846}">
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -45495,7 +49017,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -45518,7 +49040,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>144</v>
       </c>
@@ -45541,7 +49063,7 @@
         <v>0.6804</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>145</v>
       </c>
@@ -45581,17 +49103,17 @@
       <c r="M67">
         <v>0.13200000000000001</v>
       </c>
+      <c r="N67">
+        <v>6.9000000000000006E-2</v>
+      </c>
       <c r="O67">
-        <v>6.9000000000000006E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="P67">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="Q67">
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -45623,7 +49145,7 @@
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -45652,7 +49174,7 @@
         <v>0.57799999999999996</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>149</v>
       </c>
@@ -45678,7 +49200,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>150</v>
       </c>
@@ -45719,7 +49241,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>151</v>
       </c>
@@ -45754,7 +49276,7 @@
         <v>0.23519999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>152</v>
       </c>
@@ -45774,7 +49296,7 @@
         <v>2.7300000000000001E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>153</v>
       </c>
@@ -45794,7 +49316,7 @@
         <v>0.23799999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>154</v>
       </c>
@@ -45820,7 +49342,7 @@
         <v>0.13800000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>155</v>
       </c>
@@ -45840,7 +49362,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>156</v>
       </c>
@@ -45878,7 +49400,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>157</v>
       </c>
@@ -45916,7 +49438,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>158</v>
       </c>
@@ -45939,7 +49461,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -45963,642 +49485,604 @@
       <c r="B81">
         <v>6.0000000000000001E-3</v>
       </c>
+      <c r="C81">
+        <v>7.0000000000000001E-3</v>
+      </c>
       <c r="D81">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="E81">
-        <v>7.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F81">
-        <v>8.0000000000000002E-3</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G81">
-        <v>2.4E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H81">
-        <v>1.7000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I81">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="J81">
-        <v>1.2999999999999999E-2</v>
-      </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82">
-        <v>0.27</v>
+        <v>1.38</v>
       </c>
       <c r="C82">
-        <v>0.219</v>
+        <v>1.65</v>
       </c>
       <c r="D82">
-        <v>9.2999999999999999E-2</v>
+        <v>1.53</v>
       </c>
       <c r="E82">
-        <v>6.4000000000000001E-2</v>
+        <v>1.66</v>
       </c>
       <c r="F82">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G82">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="H82">
-        <v>0.02</v>
-      </c>
-      <c r="I82">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="J82">
-        <v>0.01</v>
-      </c>
-      <c r="K82">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="L82">
-        <v>8.9999999999999993E-3</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83">
-        <v>1.38</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="C83">
-        <v>1.65</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D83">
-        <v>1.53</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E83">
-        <v>1.66</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F83">
-        <v>1.65</v>
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="G83">
+        <v>0.156</v>
+      </c>
+      <c r="H83">
+        <v>0.108</v>
+      </c>
+      <c r="I83">
+        <v>0.04</v>
+      </c>
+      <c r="J83">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="K83">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L83">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="M83">
+        <v>9.2999999999999999E-2</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B84">
-        <v>8.9999999999999993E-3</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="C84">
-        <v>8.0000000000000002E-3</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="D84">
-        <v>1.0999999999999999E-2</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="E84">
-        <v>2.1000000000000001E-2</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="F84">
-        <v>9.0999999999999998E-2</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="G84">
-        <v>0.156</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="H84">
-        <v>0.108</v>
-      </c>
-      <c r="I84">
-        <v>0.04</v>
-      </c>
-      <c r="J84">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="K84">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L84">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="M84">
-        <v>9.2999999999999999E-2</v>
+        <v>0.44700000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B85">
-        <v>0.20699999999999999</v>
+        <v>0.24049999999999999</v>
       </c>
       <c r="C85">
-        <v>0.20599999999999999</v>
+        <v>0.75179999999999991</v>
       </c>
       <c r="D85">
-        <v>0.59899999999999998</v>
+        <v>1.284</v>
       </c>
       <c r="E85">
-        <v>0.52900000000000003</v>
+        <v>0.9282999999999999</v>
       </c>
       <c r="F85">
-        <v>0.69799999999999995</v>
+        <v>1.018</v>
       </c>
       <c r="G85">
-        <v>0.63200000000000001</v>
+        <v>0.80020000000000002</v>
       </c>
       <c r="H85">
-        <v>0.44700000000000001</v>
+        <v>0.49869999999999998</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B86">
-        <v>0.24049999999999999</v>
+        <v>1.1359999999999999</v>
       </c>
       <c r="C86">
-        <v>0.75179999999999991</v>
+        <v>2.835</v>
       </c>
       <c r="D86">
-        <v>1.284</v>
+        <v>2.7810000000000001</v>
       </c>
       <c r="E86">
-        <v>0.9282999999999999</v>
+        <v>1.9430000000000001</v>
       </c>
       <c r="F86">
-        <v>1.018</v>
+        <v>2.2090000000000001</v>
       </c>
       <c r="G86">
-        <v>0.80020000000000002</v>
+        <v>2.5230000000000001</v>
       </c>
       <c r="H86">
-        <v>0.49869999999999998</v>
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="I86">
+        <v>1.165</v>
+      </c>
+      <c r="J86">
+        <v>0.52729999999999999</v>
+      </c>
+      <c r="K86">
+        <v>0.25459999999999999</v>
+      </c>
+      <c r="L86">
+        <v>0.10890000000000001</v>
+      </c>
+      <c r="M86">
+        <v>5.3800000000000001E-2</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B87">
-        <v>1.1359999999999999</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="C87">
-        <v>2.835</v>
+        <v>1.49</v>
       </c>
       <c r="D87">
-        <v>2.7810000000000001</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="E87">
-        <v>1.9430000000000001</v>
+        <v>0.72399999999999998</v>
       </c>
       <c r="F87">
-        <v>2.2090000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="G87">
-        <v>2.5230000000000001</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="H87">
-        <v>1.8560000000000001</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="I87">
-        <v>1.165</v>
-      </c>
-      <c r="J87">
-        <v>0.52729999999999999</v>
-      </c>
-      <c r="K87">
-        <v>0.25459999999999999</v>
-      </c>
-      <c r="L87">
-        <v>0.10890000000000001</v>
-      </c>
-      <c r="M87">
-        <v>5.3800000000000001E-2</v>
+        <v>0.42899999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B88">
-        <v>0.55700000000000005</v>
+        <v>9.4E-2</v>
       </c>
       <c r="C88">
-        <v>1.49</v>
+        <v>0.224</v>
       </c>
       <c r="D88">
-        <v>0.66600000000000004</v>
+        <v>0.308</v>
       </c>
       <c r="E88">
-        <v>0.72399999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F88">
-        <v>0.748</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="G88">
-        <v>0.79100000000000004</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="H88">
-        <v>0.60099999999999998</v>
-      </c>
-      <c r="I88">
-        <v>0.42899999999999999</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B89">
-        <v>9.4E-2</v>
+        <v>9.7799999999999998E-2</v>
       </c>
       <c r="C89">
-        <v>0.224</v>
+        <v>7.740000000000001E-2</v>
       </c>
       <c r="D89">
-        <v>0.308</v>
+        <v>8.3699999999999997E-2</v>
       </c>
       <c r="E89">
-        <v>0.28000000000000003</v>
+        <v>6.6799999999999998E-2</v>
       </c>
       <c r="F89">
-        <v>0.32400000000000001</v>
+        <v>5.2700000000000004E-2</v>
       </c>
       <c r="G89">
-        <v>0.34200000000000003</v>
+        <v>3.61E-2</v>
       </c>
       <c r="H89">
-        <v>0.33700000000000002</v>
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="I89">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="J89">
+        <v>7.9700000000000007E-2</v>
+      </c>
+      <c r="K89">
+        <v>7.1300000000000002E-2</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B90">
-        <v>9.7799999999999998E-2</v>
+        <v>0.28370000000000001</v>
       </c>
       <c r="C90">
-        <v>7.740000000000001E-2</v>
+        <v>0.23810000000000001</v>
       </c>
       <c r="D90">
-        <v>8.3699999999999997E-2</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="E90">
-        <v>6.6799999999999998E-2</v>
+        <v>0.1835</v>
       </c>
       <c r="F90">
-        <v>5.2700000000000004E-2</v>
-      </c>
-      <c r="G90">
-        <v>3.61E-2</v>
-      </c>
-      <c r="H90">
-        <v>6.7799999999999999E-2</v>
-      </c>
-      <c r="I90">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="J90">
-        <v>7.9700000000000007E-2</v>
-      </c>
-      <c r="K90">
-        <v>7.1300000000000002E-2</v>
+        <v>0.18919999999999998</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B91">
-        <v>0.28370000000000001</v>
+        <v>0.24530000000000002</v>
       </c>
       <c r="C91">
-        <v>0.23810000000000001</v>
+        <v>0.30219999999999997</v>
       </c>
       <c r="D91">
-        <v>0.30499999999999999</v>
+        <v>0.39369999999999999</v>
       </c>
       <c r="E91">
-        <v>0.1835</v>
+        <v>0.25390000000000001</v>
       </c>
       <c r="F91">
-        <v>0.18919999999999998</v>
+        <v>0.28589999999999999</v>
+      </c>
+      <c r="G91">
+        <v>0.32430000000000003</v>
+      </c>
+      <c r="H91">
+        <v>0.1812</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B92">
-        <v>0.24530000000000002</v>
-      </c>
-      <c r="C92">
-        <v>0.30219999999999997</v>
+        <v>9.9699999999999997E-2</v>
       </c>
       <c r="D92">
-        <v>0.39369999999999999</v>
+        <v>0.46139999999999998</v>
       </c>
       <c r="E92">
-        <v>0.25390000000000001</v>
+        <v>0.38119999999999998</v>
       </c>
       <c r="F92">
-        <v>0.28589999999999999</v>
+        <v>0.4395</v>
       </c>
       <c r="G92">
-        <v>0.32430000000000003</v>
+        <v>0.49339999999999995</v>
       </c>
       <c r="H92">
-        <v>0.1812</v>
+        <v>0.47020000000000001</v>
+      </c>
+      <c r="I92">
+        <v>0.31560000000000005</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B93">
-        <v>9.9699999999999997E-2</v>
+        <v>1.1890000000000001</v>
+      </c>
+      <c r="C93">
+        <v>0.88270000000000004</v>
       </c>
       <c r="D93">
-        <v>0.46139999999999998</v>
+        <v>0.6079</v>
       </c>
       <c r="E93">
-        <v>0.38119999999999998</v>
+        <v>0.36969999999999997</v>
       </c>
       <c r="F93">
-        <v>0.4395</v>
+        <v>0.15759999999999999</v>
       </c>
       <c r="G93">
-        <v>0.49339999999999995</v>
+        <v>8.4699999999999998E-2</v>
       </c>
       <c r="H93">
-        <v>0.47020000000000001</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="I93">
-        <v>0.31560000000000005</v>
+        <v>4.0500000000000001E-2</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B94">
-        <v>1.1890000000000001</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="C94">
-        <v>0.88270000000000004</v>
+        <v>5.61</v>
       </c>
       <c r="D94">
-        <v>0.6079</v>
+        <v>6.17</v>
       </c>
       <c r="E94">
-        <v>0.36969999999999997</v>
+        <v>3.09</v>
       </c>
       <c r="F94">
-        <v>0.15759999999999999</v>
+        <v>3.16</v>
       </c>
       <c r="G94">
-        <v>8.4699999999999998E-2</v>
+        <v>3.87</v>
       </c>
       <c r="H94">
-        <v>5.9400000000000001E-2</v>
+        <v>3.79</v>
       </c>
       <c r="I94">
-        <v>4.0500000000000001E-2</v>
+        <v>3.1</v>
+      </c>
+      <c r="J94">
+        <v>1.43</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B95">
-        <v>3.5000000000000003E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="C95">
-        <v>5.61</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="D95">
-        <v>6.17</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="E95">
-        <v>3.09</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="F95">
-        <v>3.16</v>
-      </c>
-      <c r="G95">
-        <v>3.87</v>
-      </c>
-      <c r="H95">
-        <v>3.79</v>
-      </c>
-      <c r="I95">
-        <v>3.1</v>
-      </c>
-      <c r="J95">
-        <v>1.43</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B96">
-        <v>9.6000000000000002E-2</v>
+        <v>0.315</v>
       </c>
       <c r="C96">
-        <v>0.23300000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="D96">
-        <v>0.17799999999999999</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="E96">
-        <v>0.16800000000000001</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="F96">
-        <v>0.182</v>
+        <v>0.41799999999999998</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B97">
-        <v>0.315</v>
+        <v>5.4600000000000003E-2</v>
       </c>
       <c r="C97">
-        <v>0.318</v>
+        <v>5.3899999999999997E-2</v>
       </c>
       <c r="D97">
-        <v>0.26700000000000002</v>
+        <v>4.7700000000000006E-2</v>
       </c>
       <c r="E97">
-        <v>0.39400000000000002</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="F97">
-        <v>0.41799999999999998</v>
+        <v>4.4700000000000004E-2</v>
+      </c>
+      <c r="G97">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="H97">
+        <v>2.6499999999999999E-2</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B98">
-        <v>5.4600000000000003E-2</v>
+        <v>0.13319999999999999</v>
       </c>
       <c r="C98">
-        <v>5.3899999999999997E-2</v>
+        <v>0.1183</v>
       </c>
       <c r="D98">
-        <v>4.7700000000000006E-2</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="E98">
-        <v>5.9499999999999997E-2</v>
+        <v>0.17150000000000001</v>
       </c>
       <c r="F98">
-        <v>4.4700000000000004E-2</v>
-      </c>
-      <c r="G98">
-        <v>3.9600000000000003E-2</v>
-      </c>
-      <c r="H98">
-        <v>2.6499999999999999E-2</v>
+        <v>0.1512</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B99">
-        <v>0.13319999999999999</v>
+        <v>4.7E-2</v>
       </c>
       <c r="C99">
-        <v>0.1183</v>
+        <v>1.57</v>
       </c>
       <c r="D99">
-        <v>0.27900000000000003</v>
+        <v>1.52</v>
       </c>
       <c r="E99">
-        <v>0.17150000000000001</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="F99">
-        <v>0.1512</v>
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="G99">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="H99">
+        <v>0.65</v>
+      </c>
+      <c r="I99">
+        <v>0.58699999999999997</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B100">
-        <v>4.7E-2</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="C100">
-        <v>1.57</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="D100">
-        <v>1.52</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="E100">
-        <v>0.60899999999999999</v>
+        <v>1.83E-2</v>
       </c>
       <c r="F100">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="G100">
-        <v>0.68400000000000005</v>
-      </c>
-      <c r="H100">
-        <v>0.65</v>
-      </c>
-      <c r="I100">
-        <v>0.58699999999999997</v>
+        <v>2.4300000000000002E-2</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B101">
-        <v>5.4000000000000003E-3</v>
+        <v>1.7929999999999999</v>
       </c>
       <c r="C101">
-        <v>9.1999999999999998E-3</v>
+        <v>0.78379999999999994</v>
       </c>
       <c r="D101">
-        <v>2.2100000000000002E-2</v>
+        <v>0.63729999999999998</v>
       </c>
       <c r="E101">
-        <v>1.83E-2</v>
+        <v>0.5736</v>
       </c>
       <c r="F101">
-        <v>2.4300000000000002E-2</v>
+        <v>0.52960000000000007</v>
+      </c>
+      <c r="G101">
+        <v>0.66949999999999998</v>
+      </c>
+      <c r="H101">
+        <v>0.56489999999999996</v>
+      </c>
+      <c r="I101">
+        <v>0.3866</v>
+      </c>
+      <c r="J101">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K101">
+        <v>0.1517</v>
+      </c>
+      <c r="L101">
+        <v>0.1799</v>
+      </c>
+      <c r="M101">
+        <v>0.12459999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B102">
-        <v>1.7929999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="C102">
-        <v>0.78379999999999994</v>
-      </c>
-      <c r="D102">
-        <v>0.63729999999999998</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E102">
-        <v>0.5736</v>
+        <v>0.01</v>
       </c>
       <c r="F102">
-        <v>0.52960000000000007</v>
+        <v>0.01</v>
       </c>
       <c r="G102">
-        <v>0.66949999999999998</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H102">
-        <v>0.56489999999999996</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I102">
-        <v>0.3866</v>
-      </c>
-      <c r="J102">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K102">
-        <v>0.1517</v>
-      </c>
-      <c r="L102">
-        <v>0.1799</v>
-      </c>
-      <c r="M102">
-        <v>0.12459999999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>183</v>
-      </c>
-      <c r="B103">
-        <v>0.01</v>
-      </c>
-      <c r="C103">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="E103">
-        <v>0.01</v>
-      </c>
-      <c r="F103">
-        <v>0.01</v>
-      </c>
-      <c r="G103">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="H103">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I103">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -46608,6 +50092,520 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A514D442-0788-4FA9-9667-518B0697CF76}">
+  <dimension ref="A1:AC9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1" s="75" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="75" t="s">
+        <v>1649</v>
+      </c>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="72">
+        <v>7.7499999999417923</v>
+      </c>
+      <c r="C2" s="70">
+        <v>21.46666666661622</v>
+      </c>
+      <c r="D2" s="70">
+        <v>34.249999999883585</v>
+      </c>
+      <c r="E2" s="70">
+        <v>48.566666666592937</v>
+      </c>
+      <c r="F2" s="70">
+        <v>71.616666666639503</v>
+      </c>
+      <c r="G2" s="70">
+        <v>84.833333333255723</v>
+      </c>
+      <c r="H2" s="70">
+        <v>95.749999999883585</v>
+      </c>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="84">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="P2" s="84">
+        <v>2.27</v>
+      </c>
+      <c r="Q2" s="84">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="84">
+        <v>1.53</v>
+      </c>
+      <c r="S2" s="84">
+        <v>1.77</v>
+      </c>
+      <c r="T2" s="84">
+        <v>1.84</v>
+      </c>
+      <c r="U2" s="84">
+        <v>1.74</v>
+      </c>
+      <c r="V2" s="85"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="72">
+        <v>54.083333333255723</v>
+      </c>
+      <c r="C3" s="70">
+        <v>56.783333333325572</v>
+      </c>
+      <c r="D3" s="70">
+        <v>65.116666666581295</v>
+      </c>
+      <c r="E3" s="70">
+        <v>81.75</v>
+      </c>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="84">
+        <v>1.4E-2</v>
+      </c>
+      <c r="P3" s="84">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="Q3" s="84">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="R3" s="84">
+        <v>1.6E-2</v>
+      </c>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="73">
+        <v>17.566666666651145</v>
+      </c>
+      <c r="C4" s="71">
+        <v>33.700000000011642</v>
+      </c>
+      <c r="D4" s="71">
+        <v>58.833333333372138</v>
+      </c>
+      <c r="E4" s="71">
+        <v>81.383333333360497</v>
+      </c>
+      <c r="F4" s="71">
+        <v>105.86666666669771</v>
+      </c>
+      <c r="G4" s="71">
+        <v>116.90000000002328</v>
+      </c>
+      <c r="H4" s="71">
+        <v>130.1166666666395</v>
+      </c>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="84">
+        <v>0.39</v>
+      </c>
+      <c r="P4" s="84">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="Q4" s="84">
+        <v>0.73</v>
+      </c>
+      <c r="R4" s="84">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="S4" s="84">
+        <v>1.29</v>
+      </c>
+      <c r="T4" s="84">
+        <v>1.2</v>
+      </c>
+      <c r="U4" s="84">
+        <v>1.46</v>
+      </c>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="73">
+        <v>114.21666666667443</v>
+      </c>
+      <c r="C5" s="71">
+        <v>129.71666666673264</v>
+      </c>
+      <c r="D5" s="71">
+        <v>129.94999999995343</v>
+      </c>
+      <c r="E5" s="71">
+        <v>153.86666666669771</v>
+      </c>
+      <c r="F5" s="71">
+        <v>178.28333333332557</v>
+      </c>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="84">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="P5" s="84">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="Q5" s="84">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="R5" s="84">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="S5" s="84">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="73">
+        <v>18.500000000058208</v>
+      </c>
+      <c r="C6" s="71">
+        <v>33</v>
+      </c>
+      <c r="D6" s="71">
+        <v>57.149999999965075</v>
+      </c>
+      <c r="E6" s="71">
+        <v>81.500000000058208</v>
+      </c>
+      <c r="F6" s="71">
+        <v>106.26666666660458</v>
+      </c>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="84">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="P6" s="84">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="Q6" s="84">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="R6" s="84">
+        <v>0.18</v>
+      </c>
+      <c r="S6" s="84">
+        <v>0.161</v>
+      </c>
+      <c r="T6" s="85"/>
+      <c r="U6" s="85"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="85"/>
+      <c r="X6" s="85"/>
+      <c r="Y6" s="85"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="75" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="74">
+        <v>3.3499999999185093</v>
+      </c>
+      <c r="C7" s="69">
+        <v>3.3499999999185093</v>
+      </c>
+      <c r="D7" s="71">
+        <v>21.916666666686069</v>
+      </c>
+      <c r="E7" s="71">
+        <v>24.116666666697711</v>
+      </c>
+      <c r="F7" s="71">
+        <v>53.833333333313931</v>
+      </c>
+      <c r="G7" s="71">
+        <v>72.28333333338378</v>
+      </c>
+      <c r="H7" s="71">
+        <v>96.049999999988358</v>
+      </c>
+      <c r="I7" s="71">
+        <v>120.08333333325572</v>
+      </c>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="85">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="P7" s="85">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="Q7" s="85">
+        <v>7.8E-2</v>
+      </c>
+      <c r="R7" s="85">
+        <v>0.106</v>
+      </c>
+      <c r="S7" s="85">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="T7" s="85">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="U7" s="85">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="V7" s="85">
+        <v>1.9E-2</v>
+      </c>
+      <c r="W7" s="85"/>
+      <c r="X7" s="85"/>
+      <c r="Y7" s="85"/>
+      <c r="AC7" s="12"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="75" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="73">
+        <v>22.416666666744277</v>
+      </c>
+      <c r="C8" s="69">
+        <v>24.550000000046566</v>
+      </c>
+      <c r="D8" s="69">
+        <v>24.550000000046566</v>
+      </c>
+      <c r="E8" s="71">
+        <v>35.71666666661622</v>
+      </c>
+      <c r="F8" s="71">
+        <v>48.183333333407063</v>
+      </c>
+      <c r="G8" s="71">
+        <v>72.783333333267365</v>
+      </c>
+      <c r="H8" s="71">
+        <v>96.450000000069849</v>
+      </c>
+      <c r="I8" s="71">
+        <v>120.21666666667443</v>
+      </c>
+      <c r="J8" s="71">
+        <v>517.45000000001164</v>
+      </c>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="85">
+        <v>0.249</v>
+      </c>
+      <c r="P8" s="85">
+        <v>0.36</v>
+      </c>
+      <c r="Q8" s="85">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="R8" s="85">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="S8" s="85">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="T8" s="85">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="U8" s="85">
+        <v>0.251</v>
+      </c>
+      <c r="V8" s="85">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="W8" s="85">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>4.3500000000349246</v>
+      </c>
+      <c r="C9">
+        <v>4.3666666665812954</v>
+      </c>
+      <c r="D9">
+        <v>15.650000000023283</v>
+      </c>
+      <c r="E9">
+        <v>24.450000000069849</v>
+      </c>
+      <c r="F9">
+        <v>48.433333333348855</v>
+      </c>
+      <c r="G9">
+        <v>72.199999999953434</v>
+      </c>
+      <c r="H9">
+        <v>96.883333333418705</v>
+      </c>
+      <c r="I9">
+        <v>120.76666666672099</v>
+      </c>
+      <c r="J9">
+        <v>144.21666666667443</v>
+      </c>
+      <c r="K9">
+        <v>168.03333333326736</v>
+      </c>
+      <c r="L9">
+        <v>192.09999999997672</v>
+      </c>
+      <c r="M9">
+        <v>216.23333333339542</v>
+      </c>
+      <c r="N9">
+        <v>265.48333333327901</v>
+      </c>
+      <c r="O9" s="85">
+        <v>0.27</v>
+      </c>
+      <c r="P9" s="85">
+        <v>0.219</v>
+      </c>
+      <c r="Q9" s="85">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="R9" s="85">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="S9" s="85">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="T9" s="85">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="U9" s="85">
+        <v>0.02</v>
+      </c>
+      <c r="V9" s="85">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="W9" s="85">
+        <v>0.01</v>
+      </c>
+      <c r="X9" s="85">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Y9" s="85">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="O7:V7">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>"ISBLANK(B408)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O8:W8">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>"ISBLANK(B408)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F8D8E2-DEBE-40E9-B1E9-058B7B2399F1}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -49684,7 +53682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7862867E-FDD4-4FA9-B71F-442831A64B2B}">
   <dimension ref="A1:AC77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -53305,7 +57303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE7678C-49F8-438C-8607-768C4D2B550B}">
   <dimension ref="A1:AC452"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66198,2989 +70196,4 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8135EEF6-3F0F-4D63-BE5A-9CDAF45EB7F7}">
-  <dimension ref="A1:T355"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H1" t="s">
-        <v>415</v>
-      </c>
-      <c r="I1" t="s">
-        <v>416</v>
-      </c>
-      <c r="J1" t="s">
-        <v>417</v>
-      </c>
-      <c r="K1" t="s">
-        <v>418</v>
-      </c>
-      <c r="L1" s="20" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F2" t="s">
-        <v>421</v>
-      </c>
-      <c r="G2" t="s">
-        <v>422</v>
-      </c>
-      <c r="H2" t="s">
-        <v>423</v>
-      </c>
-      <c r="I2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>414</v>
-      </c>
-      <c r="D3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F3" t="s">
-        <v>428</v>
-      </c>
-      <c r="G3" t="s">
-        <v>429</v>
-      </c>
-      <c r="H3" t="s">
-        <v>430</v>
-      </c>
-      <c r="I3" t="s">
-        <v>431</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>415</v>
-      </c>
-      <c r="D4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F4" t="s">
-        <v>434</v>
-      </c>
-      <c r="G4" t="s">
-        <v>435</v>
-      </c>
-      <c r="H4" t="s">
-        <v>436</v>
-      </c>
-      <c r="I4" t="s">
-        <v>437</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" t="s">
-        <v>439</v>
-      </c>
-      <c r="F5" t="s">
-        <v>440</v>
-      </c>
-      <c r="G5" t="s">
-        <v>441</v>
-      </c>
-      <c r="H5" t="s">
-        <v>442</v>
-      </c>
-      <c r="I5" t="s">
-        <v>443</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>417</v>
-      </c>
-      <c r="D6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" t="s">
-        <v>445</v>
-      </c>
-      <c r="F6" t="s">
-        <v>446</v>
-      </c>
-      <c r="G6" t="s">
-        <v>447</v>
-      </c>
-      <c r="H6" t="s">
-        <v>448</v>
-      </c>
-      <c r="I6" t="s">
-        <v>449</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" t="s">
-        <v>451</v>
-      </c>
-      <c r="F7" t="s">
-        <v>452</v>
-      </c>
-      <c r="G7" t="s">
-        <v>453</v>
-      </c>
-      <c r="H7" t="s">
-        <v>454</v>
-      </c>
-      <c r="I7" t="s">
-        <v>455</v>
-      </c>
-      <c r="J7" t="s">
-        <v>456</v>
-      </c>
-      <c r="K7" t="s">
-        <v>457</v>
-      </c>
-      <c r="L7" t="s">
-        <v>458</v>
-      </c>
-      <c r="M7" t="s">
-        <v>459</v>
-      </c>
-      <c r="N7" t="s">
-        <v>460</v>
-      </c>
-      <c r="O7" t="s">
-        <v>461</v>
-      </c>
-      <c r="P7" t="s">
-        <v>462</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>434</v>
-      </c>
-      <c r="R7" t="s">
-        <v>436</v>
-      </c>
-      <c r="S7" t="s">
-        <v>437</v>
-      </c>
-      <c r="T7" s="20" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="D8" t="s">
-        <v>146</v>
-      </c>
-      <c r="E8" t="s">
-        <v>463</v>
-      </c>
-      <c r="F8" t="s">
-        <v>464</v>
-      </c>
-      <c r="G8" t="s">
-        <v>465</v>
-      </c>
-      <c r="H8" t="s">
-        <v>466</v>
-      </c>
-      <c r="I8" t="s">
-        <v>467</v>
-      </c>
-      <c r="J8" t="s">
-        <v>468</v>
-      </c>
-      <c r="K8" t="s">
-        <v>469</v>
-      </c>
-      <c r="L8" t="s">
-        <v>470</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>420</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" t="s">
-        <v>472</v>
-      </c>
-      <c r="F9" t="s">
-        <v>472</v>
-      </c>
-      <c r="G9" t="s">
-        <v>473</v>
-      </c>
-      <c r="H9" t="s">
-        <v>474</v>
-      </c>
-      <c r="I9" t="s">
-        <v>475</v>
-      </c>
-      <c r="J9" t="s">
-        <v>476</v>
-      </c>
-      <c r="K9" t="s">
-        <v>477</v>
-      </c>
-      <c r="L9" s="20" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>421</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" t="s">
-        <v>479</v>
-      </c>
-      <c r="F10" t="s">
-        <v>480</v>
-      </c>
-      <c r="G10" t="s">
-        <v>481</v>
-      </c>
-      <c r="H10" t="s">
-        <v>482</v>
-      </c>
-      <c r="I10" t="s">
-        <v>483</v>
-      </c>
-      <c r="J10" t="s">
-        <v>484</v>
-      </c>
-      <c r="K10" t="s">
-        <v>485</v>
-      </c>
-      <c r="L10" s="20" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>422</v>
-      </c>
-      <c r="D11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E11" t="s">
-        <v>487</v>
-      </c>
-      <c r="F11" t="s">
-        <v>488</v>
-      </c>
-      <c r="G11" t="s">
-        <v>489</v>
-      </c>
-      <c r="H11" t="s">
-        <v>490</v>
-      </c>
-      <c r="I11" t="s">
-        <v>491</v>
-      </c>
-      <c r="J11" t="s">
-        <v>492</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>423</v>
-      </c>
-      <c r="D12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>494</v>
-      </c>
-      <c r="F12" t="s">
-        <v>495</v>
-      </c>
-      <c r="G12" t="s">
-        <v>496</v>
-      </c>
-      <c r="H12" t="s">
-        <v>497</v>
-      </c>
-      <c r="I12" t="s">
-        <v>498</v>
-      </c>
-      <c r="J12" t="s">
-        <v>499</v>
-      </c>
-      <c r="K12" t="s">
-        <v>500</v>
-      </c>
-      <c r="L12" t="s">
-        <v>501</v>
-      </c>
-      <c r="M12" t="s">
-        <v>502</v>
-      </c>
-      <c r="N12" t="s">
-        <v>503</v>
-      </c>
-      <c r="O12" t="s">
-        <v>504</v>
-      </c>
-      <c r="P12" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q12" s="20" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>424</v>
-      </c>
-      <c r="D13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" t="s">
-        <v>507</v>
-      </c>
-      <c r="F13" t="s">
-        <v>508</v>
-      </c>
-      <c r="G13" t="s">
-        <v>509</v>
-      </c>
-      <c r="H13" t="s">
-        <v>510</v>
-      </c>
-      <c r="I13" t="s">
-        <v>511</v>
-      </c>
-      <c r="J13" t="s">
-        <v>512</v>
-      </c>
-      <c r="K13" t="s">
-        <v>513</v>
-      </c>
-      <c r="L13" t="s">
-        <v>514</v>
-      </c>
-      <c r="M13" t="s">
-        <v>515</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>425</v>
-      </c>
-      <c r="D14" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" t="s">
-        <v>517</v>
-      </c>
-      <c r="F14" t="s">
-        <v>518</v>
-      </c>
-      <c r="G14" t="s">
-        <v>519</v>
-      </c>
-      <c r="H14" t="s">
-        <v>520</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="D15" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" t="s">
-        <v>522</v>
-      </c>
-      <c r="F15" t="s">
-        <v>523</v>
-      </c>
-      <c r="G15" t="s">
-        <v>524</v>
-      </c>
-      <c r="H15" t="s">
-        <v>525</v>
-      </c>
-      <c r="I15" t="s">
-        <v>526</v>
-      </c>
-      <c r="J15" t="s">
-        <v>527</v>
-      </c>
-      <c r="K15" t="s">
-        <v>528</v>
-      </c>
-      <c r="L15" t="s">
-        <v>529</v>
-      </c>
-      <c r="M15" t="s">
-        <v>530</v>
-      </c>
-      <c r="N15" t="s">
-        <v>531</v>
-      </c>
-      <c r="O15" t="s">
-        <v>532</v>
-      </c>
-      <c r="P15" s="20" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" t="s">
-        <v>534</v>
-      </c>
-      <c r="F16" t="s">
-        <v>535</v>
-      </c>
-      <c r="G16" t="s">
-        <v>536</v>
-      </c>
-      <c r="H16" t="s">
-        <v>537</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>428</v>
-      </c>
-      <c r="D17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" t="s">
-        <v>539</v>
-      </c>
-      <c r="F17" t="s">
-        <v>540</v>
-      </c>
-      <c r="G17" t="s">
-        <v>485</v>
-      </c>
-      <c r="H17" t="s">
-        <v>486</v>
-      </c>
-      <c r="I17" t="s">
-        <v>541</v>
-      </c>
-      <c r="J17" t="s">
-        <v>542</v>
-      </c>
-      <c r="K17" t="s">
-        <v>543</v>
-      </c>
-      <c r="L17" t="s">
-        <v>544</v>
-      </c>
-      <c r="M17" t="s">
-        <v>545</v>
-      </c>
-      <c r="N17" t="s">
-        <v>546</v>
-      </c>
-      <c r="O17" s="20" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>429</v>
-      </c>
-      <c r="D18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" t="s">
-        <v>548</v>
-      </c>
-      <c r="F18" t="s">
-        <v>549</v>
-      </c>
-      <c r="G18" t="s">
-        <v>550</v>
-      </c>
-      <c r="H18" t="s">
-        <v>551</v>
-      </c>
-      <c r="I18" t="s">
-        <v>552</v>
-      </c>
-      <c r="J18" t="s">
-        <v>553</v>
-      </c>
-      <c r="K18" t="s">
-        <v>554</v>
-      </c>
-      <c r="L18" t="s">
-        <v>555</v>
-      </c>
-      <c r="M18" t="s">
-        <v>556</v>
-      </c>
-      <c r="N18" t="s">
-        <v>557</v>
-      </c>
-      <c r="O18" s="20" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>430</v>
-      </c>
-      <c r="D19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" t="s">
-        <v>559</v>
-      </c>
-      <c r="F19" t="s">
-        <v>560</v>
-      </c>
-      <c r="G19" t="s">
-        <v>561</v>
-      </c>
-      <c r="H19" t="s">
-        <v>562</v>
-      </c>
-      <c r="I19" t="s">
-        <v>563</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>431</v>
-      </c>
-      <c r="D20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" t="s">
-        <v>565</v>
-      </c>
-      <c r="F20" t="s">
-        <v>566</v>
-      </c>
-      <c r="G20" t="s">
-        <v>567</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="D21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" t="s">
-        <v>569</v>
-      </c>
-      <c r="F21" t="s">
-        <v>570</v>
-      </c>
-      <c r="G21" t="s">
-        <v>571</v>
-      </c>
-      <c r="H21" t="s">
-        <v>572</v>
-      </c>
-      <c r="I21" t="s">
-        <v>573</v>
-      </c>
-      <c r="J21" t="s">
-        <v>574</v>
-      </c>
-      <c r="K21" t="s">
-        <v>575</v>
-      </c>
-      <c r="L21" t="s">
-        <v>576</v>
-      </c>
-      <c r="M21" s="20" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>433</v>
-      </c>
-      <c r="D22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E22" t="s">
-        <v>578</v>
-      </c>
-      <c r="F22" t="s">
-        <v>579</v>
-      </c>
-      <c r="G22" t="s">
-        <v>580</v>
-      </c>
-      <c r="H22" t="s">
-        <v>581</v>
-      </c>
-      <c r="I22" t="s">
-        <v>582</v>
-      </c>
-      <c r="J22" t="s">
-        <v>583</v>
-      </c>
-      <c r="K22" t="s">
-        <v>584</v>
-      </c>
-      <c r="L22" t="s">
-        <v>585</v>
-      </c>
-      <c r="M22" t="s">
-        <v>586</v>
-      </c>
-      <c r="N22" t="s">
-        <v>587</v>
-      </c>
-      <c r="O22" t="s">
-        <v>588</v>
-      </c>
-      <c r="P22" t="s">
-        <v>589</v>
-      </c>
-      <c r="Q22" s="20" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>434</v>
-      </c>
-      <c r="D23" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23" t="s">
-        <v>591</v>
-      </c>
-      <c r="F23" t="s">
-        <v>592</v>
-      </c>
-      <c r="G23" t="s">
-        <v>593</v>
-      </c>
-      <c r="H23" t="s">
-        <v>549</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>435</v>
-      </c>
-      <c r="D24" t="s">
-        <v>162</v>
-      </c>
-      <c r="E24" t="s">
-        <v>595</v>
-      </c>
-      <c r="F24" t="s">
-        <v>596</v>
-      </c>
-      <c r="G24" t="s">
-        <v>597</v>
-      </c>
-      <c r="H24" t="s">
-        <v>598</v>
-      </c>
-      <c r="I24" t="s">
-        <v>599</v>
-      </c>
-      <c r="J24" t="s">
-        <v>600</v>
-      </c>
-      <c r="K24" t="s">
-        <v>601</v>
-      </c>
-      <c r="L24" t="s">
-        <v>602</v>
-      </c>
-      <c r="M24" t="s">
-        <v>603</v>
-      </c>
-      <c r="N24" t="s">
-        <v>604</v>
-      </c>
-      <c r="O24" t="s">
-        <v>605</v>
-      </c>
-      <c r="P24" s="20" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>436</v>
-      </c>
-      <c r="D25" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" t="s">
-        <v>607</v>
-      </c>
-      <c r="F25" t="s">
-        <v>608</v>
-      </c>
-      <c r="G25" t="s">
-        <v>609</v>
-      </c>
-      <c r="H25" t="s">
-        <v>610</v>
-      </c>
-      <c r="I25" t="s">
-        <v>611</v>
-      </c>
-      <c r="J25" t="s">
-        <v>612</v>
-      </c>
-      <c r="K25" s="20" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>437</v>
-      </c>
-      <c r="D26" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" t="s">
-        <v>614</v>
-      </c>
-      <c r="F26" t="s">
-        <v>615</v>
-      </c>
-      <c r="G26" t="s">
-        <v>616</v>
-      </c>
-      <c r="H26" t="s">
-        <v>617</v>
-      </c>
-      <c r="I26" t="s">
-        <v>618</v>
-      </c>
-      <c r="J26" t="s">
-        <v>619</v>
-      </c>
-      <c r="K26" s="20" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="D27" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" t="s">
-        <v>621</v>
-      </c>
-      <c r="F27" t="s">
-        <v>622</v>
-      </c>
-      <c r="G27" t="s">
-        <v>623</v>
-      </c>
-      <c r="H27" t="s">
-        <v>624</v>
-      </c>
-      <c r="I27" t="s">
-        <v>625</v>
-      </c>
-      <c r="J27" t="s">
-        <v>626</v>
-      </c>
-      <c r="K27" t="s">
-        <v>627</v>
-      </c>
-      <c r="L27" t="s">
-        <v>628</v>
-      </c>
-      <c r="M27" t="s">
-        <v>629</v>
-      </c>
-      <c r="N27" t="s">
-        <v>630</v>
-      </c>
-      <c r="O27" t="s">
-        <v>631</v>
-      </c>
-      <c r="P27" s="20" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>439</v>
-      </c>
-      <c r="D28" t="s">
-        <v>166</v>
-      </c>
-      <c r="E28" t="s">
-        <v>633</v>
-      </c>
-      <c r="F28" t="s">
-        <v>634</v>
-      </c>
-      <c r="G28" t="s">
-        <v>634</v>
-      </c>
-      <c r="H28" t="s">
-        <v>635</v>
-      </c>
-      <c r="I28" t="s">
-        <v>636</v>
-      </c>
-      <c r="J28" t="s">
-        <v>637</v>
-      </c>
-      <c r="K28" t="s">
-        <v>638</v>
-      </c>
-      <c r="L28" t="s">
-        <v>639</v>
-      </c>
-      <c r="M28" s="20" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>440</v>
-      </c>
-      <c r="D29" t="s">
-        <v>167</v>
-      </c>
-      <c r="E29" t="s">
-        <v>641</v>
-      </c>
-      <c r="F29" t="s">
-        <v>642</v>
-      </c>
-      <c r="G29" t="s">
-        <v>643</v>
-      </c>
-      <c r="H29" t="s">
-        <v>644</v>
-      </c>
-      <c r="I29" t="s">
-        <v>645</v>
-      </c>
-      <c r="J29" t="s">
-        <v>646</v>
-      </c>
-      <c r="K29" t="s">
-        <v>647</v>
-      </c>
-      <c r="L29" s="20" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>441</v>
-      </c>
-      <c r="D30" t="s">
-        <v>168</v>
-      </c>
-      <c r="E30" t="s">
-        <v>649</v>
-      </c>
-      <c r="F30" t="s">
-        <v>650</v>
-      </c>
-      <c r="G30" t="s">
-        <v>651</v>
-      </c>
-      <c r="H30" t="s">
-        <v>652</v>
-      </c>
-      <c r="I30" t="s">
-        <v>653</v>
-      </c>
-      <c r="J30" t="s">
-        <v>654</v>
-      </c>
-      <c r="K30" s="20" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>442</v>
-      </c>
-      <c r="D31" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" t="s">
-        <v>656</v>
-      </c>
-      <c r="F31" t="s">
-        <v>657</v>
-      </c>
-      <c r="G31" t="s">
-        <v>658</v>
-      </c>
-      <c r="H31" t="s">
-        <v>659</v>
-      </c>
-      <c r="I31" t="s">
-        <v>660</v>
-      </c>
-      <c r="J31" t="s">
-        <v>661</v>
-      </c>
-      <c r="K31" t="s">
-        <v>662</v>
-      </c>
-      <c r="L31" t="s">
-        <v>663</v>
-      </c>
-      <c r="M31" t="s">
-        <v>664</v>
-      </c>
-      <c r="N31" s="20" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>443</v>
-      </c>
-      <c r="D32" t="s">
-        <v>170</v>
-      </c>
-      <c r="E32" t="s">
-        <v>666</v>
-      </c>
-      <c r="F32" t="s">
-        <v>667</v>
-      </c>
-      <c r="G32" t="s">
-        <v>668</v>
-      </c>
-      <c r="H32" t="s">
-        <v>669</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="D33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E33" t="s">
-        <v>671</v>
-      </c>
-      <c r="F33" t="s">
-        <v>659</v>
-      </c>
-      <c r="G33" t="s">
-        <v>672</v>
-      </c>
-      <c r="H33" t="s">
-        <v>660</v>
-      </c>
-      <c r="I33" t="s">
-        <v>661</v>
-      </c>
-      <c r="J33" t="s">
-        <v>663</v>
-      </c>
-      <c r="K33" s="20" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>445</v>
-      </c>
-      <c r="D34" t="s">
-        <v>172</v>
-      </c>
-      <c r="E34" t="s">
-        <v>673</v>
-      </c>
-      <c r="F34" t="s">
-        <v>674</v>
-      </c>
-      <c r="G34" t="s">
-        <v>675</v>
-      </c>
-      <c r="H34" t="s">
-        <v>676</v>
-      </c>
-      <c r="I34" t="s">
-        <v>677</v>
-      </c>
-      <c r="J34" t="s">
-        <v>678</v>
-      </c>
-      <c r="K34" t="s">
-        <v>679</v>
-      </c>
-      <c r="L34" s="20" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>446</v>
-      </c>
-      <c r="D35" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" t="s">
-        <v>681</v>
-      </c>
-      <c r="F35" t="s">
-        <v>682</v>
-      </c>
-      <c r="G35" t="s">
-        <v>683</v>
-      </c>
-      <c r="H35" t="s">
-        <v>684</v>
-      </c>
-      <c r="I35" t="s">
-        <v>685</v>
-      </c>
-      <c r="J35" t="s">
-        <v>686</v>
-      </c>
-      <c r="K35" t="s">
-        <v>687</v>
-      </c>
-      <c r="L35" s="20" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>447</v>
-      </c>
-      <c r="D36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" t="s">
-        <v>689</v>
-      </c>
-      <c r="F36" t="s">
-        <v>690</v>
-      </c>
-      <c r="G36" t="s">
-        <v>691</v>
-      </c>
-      <c r="H36" t="s">
-        <v>692</v>
-      </c>
-      <c r="I36" t="s">
-        <v>693</v>
-      </c>
-      <c r="J36" t="s">
-        <v>694</v>
-      </c>
-      <c r="K36" t="s">
-        <v>695</v>
-      </c>
-      <c r="L36" t="s">
-        <v>696</v>
-      </c>
-      <c r="M36" s="20" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>448</v>
-      </c>
-      <c r="D37" t="s">
-        <v>175</v>
-      </c>
-      <c r="E37" t="s">
-        <v>698</v>
-      </c>
-      <c r="F37" t="s">
-        <v>699</v>
-      </c>
-      <c r="G37" t="s">
-        <v>700</v>
-      </c>
-      <c r="H37" t="s">
-        <v>701</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>449</v>
-      </c>
-      <c r="D38" t="s">
-        <v>176</v>
-      </c>
-      <c r="E38" t="s">
-        <v>703</v>
-      </c>
-      <c r="F38" t="s">
-        <v>704</v>
-      </c>
-      <c r="G38" t="s">
-        <v>705</v>
-      </c>
-      <c r="H38" t="s">
-        <v>537</v>
-      </c>
-      <c r="I38" s="20" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>450</v>
-      </c>
-      <c r="D39" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" t="s">
-        <v>706</v>
-      </c>
-      <c r="F39" t="s">
-        <v>707</v>
-      </c>
-      <c r="G39" t="s">
-        <v>708</v>
-      </c>
-      <c r="H39" t="s">
-        <v>709</v>
-      </c>
-      <c r="I39" t="s">
-        <v>710</v>
-      </c>
-      <c r="J39" t="s">
-        <v>711</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>451</v>
-      </c>
-      <c r="D40" t="s">
-        <v>178</v>
-      </c>
-      <c r="E40" t="s">
-        <v>713</v>
-      </c>
-      <c r="F40" t="s">
-        <v>714</v>
-      </c>
-      <c r="G40" t="s">
-        <v>715</v>
-      </c>
-      <c r="H40" t="s">
-        <v>716</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>452</v>
-      </c>
-      <c r="D41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" t="s">
-        <v>718</v>
-      </c>
-      <c r="F41" t="s">
-        <v>719</v>
-      </c>
-      <c r="G41" t="s">
-        <v>720</v>
-      </c>
-      <c r="H41" t="s">
-        <v>721</v>
-      </c>
-      <c r="I41" t="s">
-        <v>722</v>
-      </c>
-      <c r="J41" t="s">
-        <v>723</v>
-      </c>
-      <c r="K41" t="s">
-        <v>724</v>
-      </c>
-      <c r="L41" s="20" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>453</v>
-      </c>
-      <c r="D42" t="s">
-        <v>180</v>
-      </c>
-      <c r="E42" t="s">
-        <v>726</v>
-      </c>
-      <c r="F42" t="s">
-        <v>727</v>
-      </c>
-      <c r="G42" t="s">
-        <v>421</v>
-      </c>
-      <c r="H42" t="s">
-        <v>422</v>
-      </c>
-      <c r="I42" s="20" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>454</v>
-      </c>
-      <c r="D43" t="s">
-        <v>181</v>
-      </c>
-      <c r="E43" t="s">
-        <v>728</v>
-      </c>
-      <c r="F43" t="s">
-        <v>729</v>
-      </c>
-      <c r="G43" t="s">
-        <v>730</v>
-      </c>
-      <c r="H43" t="s">
-        <v>731</v>
-      </c>
-      <c r="I43" t="s">
-        <v>732</v>
-      </c>
-      <c r="J43" t="s">
-        <v>733</v>
-      </c>
-      <c r="K43" t="s">
-        <v>734</v>
-      </c>
-      <c r="L43" t="s">
-        <v>735</v>
-      </c>
-      <c r="M43" t="s">
-        <v>736</v>
-      </c>
-      <c r="N43" t="s">
-        <v>737</v>
-      </c>
-      <c r="O43" t="s">
-        <v>738</v>
-      </c>
-      <c r="P43" s="20" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>455</v>
-      </c>
-      <c r="D44" t="s">
-        <v>182</v>
-      </c>
-      <c r="E44" t="s">
-        <v>740</v>
-      </c>
-      <c r="F44" t="s">
-        <v>741</v>
-      </c>
-      <c r="G44" t="s">
-        <v>742</v>
-      </c>
-      <c r="H44" t="s">
-        <v>743</v>
-      </c>
-      <c r="I44" t="s">
-        <v>744</v>
-      </c>
-      <c r="J44" t="s">
-        <v>745</v>
-      </c>
-      <c r="K44" t="s">
-        <v>746</v>
-      </c>
-      <c r="L44" s="20" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>456</v>
-      </c>
-      <c r="D45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="20" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="20" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="20" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="20" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="20" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="20" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="20" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="20" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="20" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="20" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="20" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="20" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="20" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="20" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="20" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210" s="20" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" s="20" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" s="20" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" s="20" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" s="20" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" s="20" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263" s="20" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" s="20" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275" s="20" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" s="20" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A291" s="20" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" s="20" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A305" s="20" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A310" s="20" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A317" s="20" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A322" s="20" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A330" s="20" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A335" s="20" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A347" s="20" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A355" s="20" t="s">
-        <v>747</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>